--- a/data/merged/2026-09-23/MERGED_UK_Stick-Vacuum_2026-09-23.xlsx
+++ b/data/merged/2026-09-23/MERGED_UK_Stick-Vacuum_2026-09-23.xlsx
@@ -6546,13 +6546,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7113,50 +7113,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7482,7 +7438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -16141,40 +16097,40 @@
       <c r="B38" s="13"/>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>B0F9YPP9C3</t>
+          <t>B0GVY4FWDK</t>
         </is>
       </c>
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>INTETURE</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Shark/page/525766F4-D5DD-4FFC-8A20-92AC184FF87C?lp_asin=B0F9YPP9C3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/INTETURE/page/81A67A11-BDF9-40C2-8A10-6B3828AADF13?lp_asin=B0GVY4FWDK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Shark Disposable Hard Floor Vacuum and Mop Pad VACMOP Refill 16 Pack, WhitesWhite 1304HK200UK</t>
+          <t>Cordless Vacuum Cleaner, 650W 55KPA Stick Vacuum with Touch Screen &amp; 3.3ft Flexible Hose, Up to 70 Mins Runtime, Self-Standin</t>
         </is>
       </c>
       <c r="I38" s="14"/>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0F9YPP9C3?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GVY4FWDK?psc=1</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61y78uO9VYL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81amekLcGTL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>B0F9YPP9C3</t>
+          <t>B0GVY4FWDK</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
@@ -16188,13 +16144,13 @@
         </is>
       </c>
       <c r="O38" s="15">
-        <v>1215</v>
+        <v>13617</v>
       </c>
       <c r="P38" s="15">
-        <v>133</v>
+        <v>24097</v>
       </c>
       <c r="Q38" s="16">
-        <v>0.1</v>
+        <v>0.65</v>
       </c>
       <c r="R38" s="17" t="inlineStr">
         <is>
@@ -16203,95 +16159,103 @@
       </c>
       <c r="S38" s="18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>41</t>
         </is>
       </c>
       <c r="T38" s="15">
-        <v>2014</v>
+        <v>216</v>
       </c>
       <c r="U38" s="16">
-        <v>0.01</v>
+        <v>-0.28</v>
       </c>
       <c r="V38" s="15">
-        <v>30190</v>
+        <v>28078</v>
       </c>
       <c r="W38" s="15" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="X38" s="15">
-        <v>14990</v>
+        <v>13839</v>
       </c>
       <c r="Y38" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z38" s="20">
-        <v>12.49</v>
+        <v>129.99</v>
       </c>
       <c r="AA38"/>
       <c r="AB38"/>
       <c r="AC38" s="2"/>
       <c r="AD38" s="19">
-        <v>188</v>
+        <v>1331</v>
       </c>
       <c r="AE38" s="15">
-        <v>11</v>
+        <v>976</v>
       </c>
       <c r="AF38" s="21">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AG38" s="22">
-        <v>0.0055000000000000005</v>
+        <v>0</v>
       </c>
       <c r="AH38" s="20">
-        <v>3.2</v>
+        <v>3.72</v>
       </c>
       <c r="AI38" s="16">
-        <v>0.79</v>
+        <v>0.97</v>
       </c>
       <c r="AJ38"/>
       <c r="AK38" s="13" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="AL38" s="19">
-        <v>483</v>
+        <v>138</v>
       </c>
       <c r="AM38" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN38" s="13"/>
       <c r="AO38" s="13"/>
       <c r="AP38"/>
       <c r="AQ38" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR38" s="19">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AS38" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>LiKroa</t>
         </is>
       </c>
       <c r="AT38" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU38" s="13"/>
-      <c r="AV38" s="14"/>
-      <c r="AW38" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU38" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV38" s="14" t="inlineStr">
+        <is>
+          <t>longhuaqu guangdong 518000 CN</t>
+        </is>
+      </c>
+      <c r="AW38" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3TL6V3PPJTQHJ</t>
+        </is>
+      </c>
       <c r="AX38" s="13"/>
-      <c r="AY38" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY38" s="13"/>
       <c r="AZ38" s="13"/>
       <c r="BA38" s="13"/>
       <c r="BB38" s="13"/>
@@ -16309,49 +16273,45 @@
       <c r="BF38" s="13"/>
       <c r="BG38" s="13"/>
       <c r="BH38" s="14"/>
-      <c r="BI38" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
+      <c r="BI38" s="23"/>
       <c r="BJ38" s="23" t="inlineStr">
         <is>
-          <t>550 g</t>
+          <t>2.99 kg</t>
         </is>
       </c>
       <c r="BK38" s="23" t="inlineStr">
         <is>
-          <t>550.00 g</t>
+          <t>2.99 kg</t>
         </is>
       </c>
       <c r="BL38" s="23" t="inlineStr">
         <is>
-          <t>9.9 x 15.5 x 25.4 cm</t>
+          <t>20 x 20 x 30 cm</t>
         </is>
       </c>
       <c r="BM38" s="23" t="inlineStr">
         <is>
-          <t>9.90 x 15.50 x 25.40 cm</t>
+          <t>20.00 x 20.00 x 30.00 cm</t>
         </is>
       </c>
       <c r="BN38" s="23" t="inlineStr">
         <is>
-          <t>550 g</t>
+          <t>4.49 kg</t>
         </is>
       </c>
       <c r="BO38" s="23" t="inlineStr">
         <is>
-          <t>550.00 g</t>
+          <t>4.49 kg</t>
         </is>
       </c>
       <c r="BP38" s="23" t="inlineStr">
         <is>
-          <t>26 x 16 x 16 cm</t>
+          <t>43.9 x 33.2 x 20.6 cm</t>
         </is>
       </c>
       <c r="BQ38" s="23" t="inlineStr">
         <is>
-          <t>26.00 x 16.00 x 16.00 cm</t>
+          <t>43.90 x 33.20 x 20.60 cm</t>
         </is>
       </c>
       <c r="BR38" s="13" t="inlineStr">
@@ -16367,40 +16327,40 @@
       <c r="B39" s="13"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>B0GVY4FWDK</t>
+          <t>B0H1BHBKTC</t>
         </is>
       </c>
       <c r="D39" s="14"/>
       <c r="E39" s="14"/>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>INTETURE</t>
+          <t>SMOTURE</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/INTETURE/page/81A67A11-BDF9-40C2-8A10-6B3828AADF13?lp_asin=B0GVY4FWDK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/SMOTURE/page/C0B880AC-DBCF-4263-BE20-34B07DB6DBA9?lp_asin=B0H1BHBKTC&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>Cordless Vacuum Cleaner, 650W 55KPA Stick Vacuum with Touch Screen &amp; 3.3ft Flexible Hose, Up to 70 Mins Runtime, Self-Standin</t>
+          <t>SMOTURE Cordless Vacuum Cleaner,55KPa Powerful Stick Vacuum Cleaner with 650W Motor,70 Min Runtime,Auto Mode,Detachable Batte</t>
         </is>
       </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GVY4FWDK?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0H1BHBKTC?psc=1</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81amekLcGTL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81zaCtkHd-L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>B0GVY4FWDK</t>
+          <t>B0H1BHBKTC</t>
         </is>
       </c>
       <c r="M39" s="14" t="inlineStr">
@@ -16414,13 +16374,13 @@
         </is>
       </c>
       <c r="O39" s="15">
-        <v>13617</v>
+        <v>45710</v>
       </c>
       <c r="P39" s="15">
-        <v>24097</v>
+        <v>-26933</v>
       </c>
       <c r="Q39" s="16">
-        <v>0.65</v>
+        <v>-1.19</v>
       </c>
       <c r="R39" s="17" t="inlineStr">
         <is>
@@ -16429,17 +16389,17 @@
       </c>
       <c r="S39" s="18" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>90</t>
         </is>
       </c>
       <c r="T39" s="15">
-        <v>216</v>
+        <v>186</v>
       </c>
       <c r="U39" s="16">
-        <v>-0.28</v>
+        <v>-0.63</v>
       </c>
       <c r="V39" s="15">
-        <v>28078</v>
+        <v>27898</v>
       </c>
       <c r="W39" s="15" t="inlineStr">
         <is>
@@ -16447,43 +16407,43 @@
         </is>
       </c>
       <c r="X39" s="15">
-        <v>13839</v>
+        <v>17358</v>
       </c>
       <c r="Y39" s="19">
         <v>2</v>
       </c>
       <c r="Z39" s="20">
-        <v>129.99</v>
+        <v>149.99</v>
       </c>
       <c r="AA39"/>
       <c r="AB39"/>
       <c r="AC39" s="2"/>
       <c r="AD39" s="19">
-        <v>1331</v>
+        <v>4181</v>
       </c>
       <c r="AE39" s="15">
-        <v>976</v>
+        <v>3983</v>
       </c>
       <c r="AF39" s="21">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AG39" s="22">
         <v>0</v>
       </c>
       <c r="AH39" s="20">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="AI39" s="16">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="AJ39"/>
       <c r="AK39" s="13" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AL39" s="19">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="AM39" s="13" t="inlineStr">
         <is>
@@ -16501,7 +16461,7 @@
       </c>
       <c r="AS39" s="14" t="inlineStr">
         <is>
-          <t>LiKroa</t>
+          <t>Graeng</t>
         </is>
       </c>
       <c r="AT39" s="13" t="inlineStr">
@@ -16516,16 +16476,20 @@
       </c>
       <c r="AV39" s="14" t="inlineStr">
         <is>
-          <t>longhuaqu guangdong 518000 CN</t>
+          <t>深圳市 广东 518000 CN</t>
         </is>
       </c>
       <c r="AW39" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3TL6V3PPJTQHJ</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AN9MVBN9OI7JL</t>
         </is>
       </c>
       <c r="AX39" s="13"/>
-      <c r="AY39" s="13"/>
+      <c r="AY39" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ39" s="13"/>
       <c r="BA39" s="13"/>
       <c r="BB39" s="13"/>
@@ -16543,45 +16507,49 @@
       <c r="BF39" s="13"/>
       <c r="BG39" s="13"/>
       <c r="BH39" s="14"/>
-      <c r="BI39" s="23"/>
+      <c r="BI39" s="23" t="inlineStr">
+        <is>
+          <t>Amazon's Choice</t>
+        </is>
+      </c>
       <c r="BJ39" s="23" t="inlineStr">
         <is>
-          <t>2.99 kg</t>
+          <t>1.8 kg</t>
         </is>
       </c>
       <c r="BK39" s="23" t="inlineStr">
         <is>
-          <t>2.99 kg</t>
+          <t>1.80 kg</t>
         </is>
       </c>
       <c r="BL39" s="23" t="inlineStr">
         <is>
-          <t>20 x 20 x 30 cm</t>
+          <t>2.5 x 2.5 x 2.5 cm</t>
         </is>
       </c>
       <c r="BM39" s="23" t="inlineStr">
         <is>
-          <t>20.00 x 20.00 x 30.00 cm</t>
+          <t>2.50 x 2.50 x 2.50 cm</t>
         </is>
       </c>
       <c r="BN39" s="23" t="inlineStr">
         <is>
-          <t>4.49 kg</t>
+          <t>4.17 kg</t>
         </is>
       </c>
       <c r="BO39" s="23" t="inlineStr">
         <is>
-          <t>4.49 kg</t>
+          <t>4.17 kg</t>
         </is>
       </c>
       <c r="BP39" s="23" t="inlineStr">
         <is>
-          <t>43.9 x 33.2 x 20.6 cm</t>
+          <t>44.9 x 32.7 x 16.4 cm</t>
         </is>
       </c>
       <c r="BQ39" s="23" t="inlineStr">
         <is>
-          <t>43.90 x 33.20 x 20.60 cm</t>
+          <t>44.90 x 32.70 x 16.40 cm</t>
         </is>
       </c>
       <c r="BR39" s="13" t="inlineStr">
@@ -16597,40 +16565,40 @@
       <c r="B40" s="13"/>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>B0H1BHBKTC</t>
+          <t>B0H1WC1PJ1</t>
         </is>
       </c>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>SMOTURE</t>
+          <t>Proscenic</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/SMOTURE/page/C0B880AC-DBCF-4263-BE20-34B07DB6DBA9?lp_asin=B0H1BHBKTC&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/stores/PROSCENIC/page/9D6AA08D-8BCB-40F7-A698-933D705EEDDF?lp_asin=B0H1WC1PJ1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>SMOTURE Cordless Vacuum Cleaner,55KPa Powerful Stick Vacuum Cleaner with 650W Motor,70 Min Runtime,Auto Mode,Detachable Batte</t>
+          <t>Proscenic P15+ Cordless Vacuum Cleaner, 70Kpa, 70-Minute Runtime, Pet Hairs600W Power, Detachable Battery, Telescopic Tube,</t>
         </is>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0H1BHBKTC?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0H1WC1PJ1?psc=1</t>
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81zaCtkHd-L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61xgSdYZzpL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>B0H1BHBKTC</t>
+          <t>B0H1WC1PJ1</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
@@ -16644,13 +16612,13 @@
         </is>
       </c>
       <c r="O40" s="15">
-        <v>45710</v>
+        <v>13660</v>
       </c>
       <c r="P40" s="15">
-        <v>-26933</v>
+        <v>34442</v>
       </c>
       <c r="Q40" s="16">
-        <v>-1.19</v>
+        <v>0.72</v>
       </c>
       <c r="R40" s="17" t="inlineStr">
         <is>
@@ -16659,17 +16627,17 @@
       </c>
       <c r="S40" s="18" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>41</t>
         </is>
       </c>
       <c r="T40" s="15">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="U40" s="16">
-        <v>-0.63</v>
+        <v>-0.21</v>
       </c>
       <c r="V40" s="15">
-        <v>27898</v>
+        <v>25338</v>
       </c>
       <c r="W40" s="15" t="inlineStr">
         <is>
@@ -16677,25 +16645,25 @@
         </is>
       </c>
       <c r="X40" s="15">
-        <v>17358</v>
+        <v>10834</v>
       </c>
       <c r="Y40" s="19">
         <v>2</v>
       </c>
       <c r="Z40" s="20">
-        <v>149.99</v>
+        <v>139.99</v>
       </c>
       <c r="AA40"/>
       <c r="AB40"/>
       <c r="AC40" s="2"/>
       <c r="AD40" s="19">
-        <v>4181</v>
+        <v>18</v>
       </c>
       <c r="AE40" s="15">
-        <v>3983</v>
+        <v>0</v>
       </c>
       <c r="AF40" s="21">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AG40" s="22">
         <v>0</v>
@@ -16704,12 +16672,12 @@
         <v>3.71</v>
       </c>
       <c r="AI40" s="16">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="AJ40"/>
       <c r="AK40" s="13" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AL40" s="19">
@@ -16717,7 +16685,7 @@
       </c>
       <c r="AM40" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN40" s="13"/>
@@ -16727,39 +16695,23 @@
         <v>10</v>
       </c>
       <c r="AR40" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS40" s="14" t="inlineStr">
         <is>
-          <t>Graeng</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT40" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU40" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV40" s="14" t="inlineStr">
-        <is>
-          <t>深圳市 广东 518000 CN</t>
-        </is>
-      </c>
-      <c r="AW40" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AN9MVBN9OI7JL</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU40" s="13"/>
+      <c r="AV40" s="14"/>
+      <c r="AW40" s="13"/>
       <c r="AX40" s="13"/>
-      <c r="AY40" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY40" s="13"/>
       <c r="AZ40" s="13"/>
       <c r="BA40" s="13"/>
       <c r="BB40" s="13"/>
@@ -16777,49 +16729,45 @@
       <c r="BF40" s="13"/>
       <c r="BG40" s="13"/>
       <c r="BH40" s="14"/>
-      <c r="BI40" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
+      <c r="BI40" s="23"/>
       <c r="BJ40" s="23" t="inlineStr">
         <is>
-          <t>1.8 kg</t>
+          <t>4.1 kg</t>
         </is>
       </c>
       <c r="BK40" s="23" t="inlineStr">
         <is>
-          <t>1.80 kg</t>
+          <t>4.10 kg</t>
         </is>
       </c>
       <c r="BL40" s="23" t="inlineStr">
         <is>
-          <t>2.5 x 2.5 x 2.5 cm</t>
+          <t>25.7 x 24.5 x 116.5 cm</t>
         </is>
       </c>
       <c r="BM40" s="23" t="inlineStr">
         <is>
-          <t>2.50 x 2.50 x 2.50 cm</t>
+          <t>25.70 x 24.50 x 116.50 cm</t>
         </is>
       </c>
       <c r="BN40" s="23" t="inlineStr">
         <is>
-          <t>4.17 kg</t>
+          <t>4.1 kg</t>
         </is>
       </c>
       <c r="BO40" s="23" t="inlineStr">
         <is>
-          <t>4.17 kg</t>
+          <t>4.10 kg</t>
         </is>
       </c>
       <c r="BP40" s="23" t="inlineStr">
         <is>
-          <t>44.9 x 32.7 x 16.4 cm</t>
+          <t>44.5 x 32.9 x 19.4 cm</t>
         </is>
       </c>
       <c r="BQ40" s="23" t="inlineStr">
         <is>
-          <t>44.90 x 32.70 x 16.40 cm</t>
+          <t>44.50 x 32.90 x 19.40 cm</t>
         </is>
       </c>
       <c r="BR40" s="13" t="inlineStr">
@@ -16835,40 +16783,40 @@
       <c r="B41" s="13"/>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>B0H1WC1PJ1</t>
+          <t>B09RMQ1XLL</t>
         </is>
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
       <c r="F41" s="14" t="inlineStr">
         <is>
-          <t>Proscenic</t>
+          <t>VYTRONIX</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/PROSCENIC/page/9D6AA08D-8BCB-40F7-A698-933D705EEDDF?lp_asin=B0H1WC1PJ1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/VYTRONIX/page/0488BBB4-7668-4BD9-83CC-3C85540B802C?lp_asin=B09RMQ1XLL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>Proscenic P15+ Cordless Vacuum Cleaner, 70Kpa, 70-Minute Runtime, Pet Hairs600W Power, Detachable Battery, Telescopic Tube,</t>
+          <t>VYTRONIX HSV3 Upright Vacuum CleanersLightweight 3-in-1 Compact Powerful Multifunction Corded Stick &amp; Handheld Vacuum | 600</t>
         </is>
       </c>
       <c r="I41" s="14"/>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0H1WC1PJ1?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B09RMQ1XLL?psc=1</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61xgSdYZzpL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51QJB9vzthL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>B0H1WC1PJ1</t>
+          <t>B09RMQ1XLL</t>
         </is>
       </c>
       <c r="M41" s="14" t="inlineStr">
@@ -16882,13 +16830,13 @@
         </is>
       </c>
       <c r="O41" s="15">
-        <v>13660</v>
+        <v>5779</v>
       </c>
       <c r="P41" s="15">
-        <v>34442</v>
+        <v>567</v>
       </c>
       <c r="Q41" s="16">
-        <v>0.72</v>
+        <v>0.09</v>
       </c>
       <c r="R41" s="17" t="inlineStr">
         <is>
@@ -16897,65 +16845,65 @@
       </c>
       <c r="S41" s="18" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>21</t>
         </is>
       </c>
       <c r="T41" s="15">
-        <v>181</v>
+        <v>747</v>
       </c>
       <c r="U41" s="16">
-        <v>-0.21</v>
+        <v>0.41</v>
       </c>
       <c r="V41" s="15">
-        <v>25338</v>
+        <v>24644</v>
       </c>
       <c r="W41" s="15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>600</t>
         </is>
       </c>
       <c r="X41" s="15">
-        <v>10834</v>
+        <v>19674</v>
       </c>
       <c r="Y41" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z41" s="20">
-        <v>139.99</v>
+        <v>32.99</v>
       </c>
       <c r="AA41"/>
       <c r="AB41"/>
       <c r="AC41" s="2"/>
       <c r="AD41" s="19">
-        <v>18</v>
+        <v>4167</v>
       </c>
       <c r="AE41" s="15">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AF41" s="21">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="AG41" s="22">
-        <v>0</v>
+        <v>0.0281</v>
       </c>
       <c r="AH41" s="20">
-        <v>3.71</v>
+        <v>4.87</v>
       </c>
       <c r="AI41" s="16">
-        <v>0.97</v>
+        <v>0.85</v>
       </c>
       <c r="AJ41"/>
       <c r="AK41" s="13" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="AL41" s="19">
-        <v>119</v>
+        <v>1679</v>
       </c>
       <c r="AM41" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN41" s="13"/>
@@ -16969,19 +16917,35 @@
       </c>
       <c r="AS41" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Vytronix</t>
         </is>
       </c>
       <c r="AT41" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU41" s="13"/>
-      <c r="AV41" s="14"/>
-      <c r="AW41" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU41" s="13" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="AV41" s="14" t="inlineStr">
+        <is>
+          <t>Dunstable Bedfordshire LU5 5UL GB</t>
+        </is>
+      </c>
+      <c r="AW41" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZNUHI65TJJP2</t>
+        </is>
+      </c>
       <c r="AX41" s="13"/>
-      <c r="AY41" s="13"/>
+      <c r="AY41" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ41" s="13"/>
       <c r="BA41" s="13"/>
       <c r="BB41" s="13"/>
@@ -16990,59 +16954,59 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD41" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD41" s="13"/>
       <c r="BE41" s="13"/>
       <c r="BF41" s="13"/>
       <c r="BG41" s="13"/>
       <c r="BH41" s="14"/>
-      <c r="BI41" s="23"/>
+      <c r="BI41" s="23" t="inlineStr">
+        <is>
+          <t>Amazon's Choice</t>
+        </is>
+      </c>
       <c r="BJ41" s="23" t="inlineStr">
         <is>
-          <t>4.1 kg</t>
+          <t>2.5 kg</t>
         </is>
       </c>
       <c r="BK41" s="23" t="inlineStr">
         <is>
-          <t>4.10 kg</t>
+          <t>2.50 kg</t>
         </is>
       </c>
       <c r="BL41" s="23" t="inlineStr">
         <is>
-          <t>25.7 x 24.5 x 116.5 cm</t>
+          <t>31 x 11 x 21 cm</t>
         </is>
       </c>
       <c r="BM41" s="23" t="inlineStr">
         <is>
-          <t>25.70 x 24.50 x 116.50 cm</t>
+          <t>31.00 x 11.00 x 21.00 cm</t>
         </is>
       </c>
       <c r="BN41" s="23" t="inlineStr">
         <is>
-          <t>4.1 kg</t>
+          <t>2.71 kg</t>
         </is>
       </c>
       <c r="BO41" s="23" t="inlineStr">
         <is>
-          <t>4.10 kg</t>
+          <t>2.71 kg</t>
         </is>
       </c>
       <c r="BP41" s="23" t="inlineStr">
         <is>
-          <t>44.5 x 32.9 x 19.4 cm</t>
+          <t>46 x 23.1 x 16.5 cm</t>
         </is>
       </c>
       <c r="BQ41" s="23" t="inlineStr">
         <is>
-          <t>44.50 x 32.90 x 19.40 cm</t>
+          <t>46.00 x 23.10 x 16.50 cm</t>
         </is>
       </c>
       <c r="BR41" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -17053,40 +17017,40 @@
       <c r="B42" s="13"/>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>B09RMQ1XLL</t>
+          <t>B0H2J8QH51</t>
         </is>
       </c>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>VYTRONIX</t>
+          <t>VACTechPro</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/VYTRONIX/page/0488BBB4-7668-4BD9-83CC-3C85540B802C?lp_asin=B09RMQ1XLL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/stores/VACTechPro/page/A2AA5919-757D-4EB7-AE3F-8644C68C4115?lp_asin=B0H2J8QH51&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>VYTRONIX HSV3 Upright Vacuum CleanersLightweight 3-in-1 Compact Powerful Multifunction Corded Stick &amp; Handheld Vacuum | 600</t>
+          <t>VACTechPro F02 Lite Cordless Vacuum Cleaner, 40KPa/450W, Self-StandingsAnti-Tangle Stick Vacuum, Powerful &amp; Lightweight, An</t>
         </is>
       </c>
       <c r="I42" s="14"/>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B09RMQ1XLL?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0H2J8QH51?psc=1</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51QJB9vzthL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41LbZ7ZgbSL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>B09RMQ1XLL</t>
+          <t>B0H2J8QH51</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
@@ -17100,13 +17064,13 @@
         </is>
       </c>
       <c r="O42" s="15">
-        <v>5779</v>
+        <v>5117</v>
       </c>
       <c r="P42" s="15">
-        <v>567</v>
+        <v>66783</v>
       </c>
       <c r="Q42" s="16">
-        <v>0.09</v>
+        <v>0.93</v>
       </c>
       <c r="R42" s="17" t="inlineStr">
         <is>
@@ -17115,61 +17079,61 @@
       </c>
       <c r="S42" s="18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>95</t>
         </is>
       </c>
       <c r="T42" s="15">
-        <v>747</v>
+        <v>308</v>
       </c>
       <c r="U42" s="16">
-        <v>0.41</v>
+        <v>-0.09</v>
       </c>
       <c r="V42" s="15">
-        <v>24644</v>
+        <v>24637</v>
       </c>
       <c r="W42" s="15" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>50</t>
         </is>
       </c>
       <c r="X42" s="15">
-        <v>19674</v>
+        <v>4000</v>
       </c>
       <c r="Y42" s="19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z42" s="20">
-        <v>32.99</v>
+        <v>79.99</v>
       </c>
       <c r="AA42"/>
       <c r="AB42"/>
       <c r="AC42" s="2"/>
       <c r="AD42" s="19">
-        <v>4167</v>
+        <v>24</v>
       </c>
       <c r="AE42" s="15">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AF42" s="21">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AG42" s="22">
-        <v>0.0281</v>
+        <v>0.11689999999999999</v>
       </c>
       <c r="AH42" s="20">
-        <v>4.87</v>
+        <v>3.71</v>
       </c>
       <c r="AI42" s="16">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="AJ42"/>
       <c r="AK42" s="13" t="inlineStr">
         <is>
-          <t>2022-02-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AL42" s="19">
-        <v>1679</v>
+        <v>96</v>
       </c>
       <c r="AM42" s="13" t="inlineStr">
         <is>
@@ -17183,11 +17147,11 @@
         <v>10</v>
       </c>
       <c r="AR42" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS42" s="14" t="inlineStr">
         <is>
-          <t>Vytronix</t>
+          <t>HUIZHENG TECO</t>
         </is>
       </c>
       <c r="AT42" s="13" t="inlineStr">
@@ -17197,25 +17161,21 @@
       </c>
       <c r="AU42" s="13" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV42" s="14" t="inlineStr">
         <is>
-          <t>Dunstable Bedfordshire LU5 5UL GB</t>
+          <t>WAN CHAI 999077 HK</t>
         </is>
       </c>
       <c r="AW42" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZNUHI65TJJP2</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A14OQRLFZKKYSN</t>
         </is>
       </c>
       <c r="AX42" s="13"/>
-      <c r="AY42" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY42" s="13"/>
       <c r="AZ42" s="13"/>
       <c r="BA42" s="13"/>
       <c r="BB42" s="13"/>
@@ -17224,59 +17184,55 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD42" s="13"/>
+      <c r="BD42" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE42" s="13"/>
       <c r="BF42" s="13"/>
       <c r="BG42" s="13"/>
       <c r="BH42" s="14"/>
-      <c r="BI42" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
+      <c r="BI42" s="23"/>
       <c r="BJ42" s="23" t="inlineStr">
         <is>
-          <t>2.5 kg</t>
+          <t>3.24 kg</t>
         </is>
       </c>
       <c r="BK42" s="23" t="inlineStr">
         <is>
-          <t>2.50 kg</t>
+          <t>3.24 kg</t>
         </is>
       </c>
       <c r="BL42" s="23" t="inlineStr">
         <is>
-          <t>31 x 11 x 21 cm</t>
-        </is>
-      </c>
-      <c r="BM42" s="23" t="inlineStr">
-        <is>
-          <t>31.00 x 11.00 x 21.00 cm</t>
-        </is>
-      </c>
+          <t>35L x 15W x 22H centimetres</t>
+        </is>
+      </c>
+      <c r="BM42" s="23"/>
       <c r="BN42" s="23" t="inlineStr">
         <is>
-          <t>2.71 kg</t>
+          <t>3.24 kg</t>
         </is>
       </c>
       <c r="BO42" s="23" t="inlineStr">
         <is>
-          <t>2.71 kg</t>
+          <t>3.24 kg</t>
         </is>
       </c>
       <c r="BP42" s="23" t="inlineStr">
         <is>
-          <t>46 x 23.1 x 16.5 cm</t>
+          <t>40.1 x 27.6 x 18.4 cm</t>
         </is>
       </c>
       <c r="BQ42" s="23" t="inlineStr">
         <is>
-          <t>46.00 x 23.10 x 16.50 cm</t>
+          <t>40.10 x 27.60 x 18.40 cm</t>
         </is>
       </c>
       <c r="BR42" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -17287,40 +17243,40 @@
       <c r="B43" s="13"/>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>B0H2J8QH51</t>
+          <t>B0G1YQ9T93</t>
         </is>
       </c>
       <c r="D43" s="14"/>
       <c r="E43" s="14"/>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>VACTechPro</t>
+          <t>Levoit</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/VACTechPro/page/A2AA5919-757D-4EB7-AE3F-8644C68C4115?lp_asin=B0H2J8QH51&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/stores/Levoit/page/774A68E1-06B2-417A-85EE-3C62CCE4C91C?lp_asin=B0G1YQ9T93&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>VACTechPro F02 Lite Cordless Vacuum Cleaner, 40KPa/450W, Self-StandingsAnti-Tangle Stick Vacuum, Powerful &amp; Lightweight, An</t>
+          <t>Levoit Cordless Vacuum Cleaner, Anti-Hair Wrap, 100,000 RPM Brushless Motors99.7% Hard Floor Clean, Up to 50 Min Runtime, 5</t>
         </is>
       </c>
       <c r="I43" s="14"/>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0H2J8QH51?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0G1YQ9T93?psc=1</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41LbZ7ZgbSL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61GsdjWeYnL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>B0H2J8QH51</t>
+          <t>B0G1YQ9T93</t>
         </is>
       </c>
       <c r="M43" s="14" t="inlineStr">
@@ -17334,13 +17290,13 @@
         </is>
       </c>
       <c r="O43" s="15">
-        <v>5117</v>
+        <v>17938</v>
       </c>
       <c r="P43" s="15">
-        <v>66783</v>
+        <v>3613</v>
       </c>
       <c r="Q43" s="16">
-        <v>0.93</v>
+        <v>0.17</v>
       </c>
       <c r="R43" s="17" t="inlineStr">
         <is>
@@ -17349,65 +17305,65 @@
       </c>
       <c r="S43" s="18" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>51</t>
         </is>
       </c>
       <c r="T43" s="15">
-        <v>308</v>
+        <v>222</v>
       </c>
       <c r="U43" s="16">
-        <v>-0.09</v>
+        <v>-0.12</v>
       </c>
       <c r="V43" s="15">
-        <v>24637</v>
+        <v>24413</v>
       </c>
       <c r="W43" s="15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="X43" s="15">
-        <v>4000</v>
+        <v>11208</v>
       </c>
       <c r="Y43" s="19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z43" s="20">
-        <v>79.99</v>
+        <v>109.97</v>
       </c>
       <c r="AA43"/>
       <c r="AB43"/>
       <c r="AC43" s="2"/>
       <c r="AD43" s="19">
-        <v>24</v>
+        <v>4883</v>
       </c>
       <c r="AE43" s="15">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AF43" s="21">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AG43" s="22">
-        <v>0.11689999999999999</v>
+        <v>0</v>
       </c>
       <c r="AH43" s="20">
         <v>3.71</v>
       </c>
       <c r="AI43" s="16">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="AJ43"/>
       <c r="AK43" s="13" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="AL43" s="19">
-        <v>96</v>
+        <v>306</v>
       </c>
       <c r="AM43" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN43" s="13"/>
@@ -17417,35 +17373,27 @@
         <v>10</v>
       </c>
       <c r="AR43" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS43" s="14" t="inlineStr">
         <is>
-          <t>HUIZHENG TECO</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT43" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU43" s="13" t="inlineStr">
-        <is>
-          <t>CN(HK)</t>
-        </is>
-      </c>
-      <c r="AV43" s="14" t="inlineStr">
-        <is>
-          <t>WAN CHAI 999077 HK</t>
-        </is>
-      </c>
-      <c r="AW43" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A14OQRLFZKKYSN</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU43" s="13"/>
+      <c r="AV43" s="14"/>
+      <c r="AW43" s="13"/>
       <c r="AX43" s="13"/>
-      <c r="AY43" s="13"/>
+      <c r="AY43" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ43" s="13"/>
       <c r="BA43" s="13"/>
       <c r="BB43" s="13"/>
@@ -17463,41 +17411,49 @@
       <c r="BF43" s="13"/>
       <c r="BG43" s="13"/>
       <c r="BH43" s="14"/>
-      <c r="BI43" s="23"/>
+      <c r="BI43" s="23" t="inlineStr">
+        <is>
+          <t>Amazon's Choice</t>
+        </is>
+      </c>
       <c r="BJ43" s="23" t="inlineStr">
         <is>
-          <t>3.24 kg</t>
+          <t>2.79 kg</t>
         </is>
       </c>
       <c r="BK43" s="23" t="inlineStr">
         <is>
-          <t>3.24 kg</t>
+          <t>2.79 kg</t>
         </is>
       </c>
       <c r="BL43" s="23" t="inlineStr">
         <is>
-          <t>35L x 15W x 22H centimetres</t>
-        </is>
-      </c>
-      <c r="BM43" s="23"/>
+          <t>110 x 19.5 x 25 cm</t>
+        </is>
+      </c>
+      <c r="BM43" s="23" t="inlineStr">
+        <is>
+          <t>110.00 x 19.50 x 25.00 cm</t>
+        </is>
+      </c>
       <c r="BN43" s="23" t="inlineStr">
         <is>
-          <t>3.24 kg</t>
+          <t>4.69 kg</t>
         </is>
       </c>
       <c r="BO43" s="23" t="inlineStr">
         <is>
-          <t>3.24 kg</t>
+          <t>4.69 kg</t>
         </is>
       </c>
       <c r="BP43" s="23" t="inlineStr">
         <is>
-          <t>40.1 x 27.6 x 18.4 cm</t>
+          <t>44.9 x 33.7 x 19 cm</t>
         </is>
       </c>
       <c r="BQ43" s="23" t="inlineStr">
         <is>
-          <t>40.10 x 27.60 x 18.40 cm</t>
+          <t>44.90 x 33.70 x 19.00 cm</t>
         </is>
       </c>
       <c r="BR43" s="13" t="inlineStr">
@@ -17513,40 +17469,40 @@
       <c r="B44" s="13"/>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>B0G1YQ9T93</t>
+          <t>B0FH4QN7S1</t>
         </is>
       </c>
       <c r="D44" s="14"/>
       <c r="E44" s="14"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>Levoit</t>
+          <t>Akitas</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Levoit/page/774A68E1-06B2-417A-85EE-3C62CCE4C91C?lp_asin=B0G1YQ9T93&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/Akitas/page/BE01E01C-FB27-4053-9F09-4CEDBCF3376A?lp_asin=B0FH4QN7S1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Levoit Cordless Vacuum Cleaner, Anti-Hair Wrap, 100,000 RPM Brushless Motors99.7% Hard Floor Clean, Up to 50 Min Runtime, 5</t>
+          <t>Akitas U10 Cordless Vacuum Cleaner – 2-in-1 Stick &amp; Handheld Design with Auto-Charging Docking station, Lightweight 2.4kg, Fo</t>
         </is>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0G1YQ9T93?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FH4QN7S1?psc=1</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61GsdjWeYnL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61iXQi6Bc8L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>B0G1YQ9T93</t>
+          <t>B0FH4QN7S1</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
@@ -17560,13 +17516,13 @@
         </is>
       </c>
       <c r="O44" s="15">
-        <v>17938</v>
+        <v>6487</v>
       </c>
       <c r="P44" s="15">
-        <v>3613</v>
+        <v>1932</v>
       </c>
       <c r="Q44" s="16">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="R44" s="17" t="inlineStr">
         <is>
@@ -17575,65 +17531,67 @@
       </c>
       <c r="S44" s="18" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T44" s="15">
-        <v>222</v>
+        <v>368</v>
       </c>
       <c r="U44" s="16">
-        <v>-0.12</v>
+        <v>-0.81</v>
       </c>
       <c r="V44" s="15">
-        <v>24413</v>
+        <v>24284</v>
       </c>
       <c r="W44" s="15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X44" s="15">
-        <v>11208</v>
+        <v>12300</v>
       </c>
       <c r="Y44" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z44" s="20">
-        <v>109.97</v>
+        <v>65.99</v>
       </c>
       <c r="AA44"/>
       <c r="AB44"/>
-      <c r="AC44" s="2"/>
+      <c r="AC44" s="2">
+        <v>20</v>
+      </c>
       <c r="AD44" s="19">
-        <v>4883</v>
+        <v>557</v>
       </c>
       <c r="AE44" s="15">
-        <v>0</v>
+        <v>397</v>
       </c>
       <c r="AF44" s="21">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AG44" s="22">
         <v>0</v>
       </c>
       <c r="AH44" s="20">
-        <v>3.71</v>
+        <v>5.43</v>
       </c>
       <c r="AI44" s="16">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="AJ44"/>
       <c r="AK44" s="13" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AL44" s="19">
-        <v>306</v>
+        <v>388</v>
       </c>
       <c r="AM44" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN44" s="13"/>
@@ -17647,17 +17605,29 @@
       </c>
       <c r="AS44" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Chelsea &amp; Co</t>
         </is>
       </c>
       <c r="AT44" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU44" s="13"/>
-      <c r="AV44" s="14"/>
-      <c r="AW44" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU44" s="13" t="inlineStr">
+        <is>
+          <t>CN(HK)</t>
+        </is>
+      </c>
+      <c r="AV44" s="14" t="inlineStr">
+        <is>
+          <t>Tin Hau Hong Kong 852 HK</t>
+        </is>
+      </c>
+      <c r="AW44" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P</t>
+        </is>
+      </c>
       <c r="AX44" s="13"/>
       <c r="AY44" s="13" t="inlineStr">
         <is>
@@ -17672,11 +17642,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD44" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD44" s="13"/>
       <c r="BE44" s="13"/>
       <c r="BF44" s="13"/>
       <c r="BG44" s="13"/>
@@ -17688,47 +17654,47 @@
       </c>
       <c r="BJ44" s="23" t="inlineStr">
         <is>
-          <t>2.79 kg</t>
+          <t>2.15 kg</t>
         </is>
       </c>
       <c r="BK44" s="23" t="inlineStr">
         <is>
-          <t>2.79 kg</t>
+          <t>2.15 kg</t>
         </is>
       </c>
       <c r="BL44" s="23" t="inlineStr">
         <is>
-          <t>110 x 19.5 x 25 cm</t>
+          <t>28 x 24 x 100 cm</t>
         </is>
       </c>
       <c r="BM44" s="23" t="inlineStr">
         <is>
-          <t>110.00 x 19.50 x 25.00 cm</t>
+          <t>28.00 x 24.00 x 100.00 cm</t>
         </is>
       </c>
       <c r="BN44" s="23" t="inlineStr">
         <is>
-          <t>4.69 kg</t>
+          <t>3.43 kg</t>
         </is>
       </c>
       <c r="BO44" s="23" t="inlineStr">
         <is>
-          <t>4.69 kg</t>
+          <t>3.43 kg</t>
         </is>
       </c>
       <c r="BP44" s="23" t="inlineStr">
         <is>
-          <t>44.9 x 33.7 x 19 cm</t>
+          <t>56.6 x 25.7 x 22 cm</t>
         </is>
       </c>
       <c r="BQ44" s="23" t="inlineStr">
         <is>
-          <t>44.90 x 33.70 x 19.00 cm</t>
+          <t>56.60 x 25.70 x 22.00 cm</t>
         </is>
       </c>
       <c r="BR44" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -17739,40 +17705,40 @@
       <c r="B45" s="13"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>B0FH4QN7S1</t>
+          <t>B0FT7BQ1P4</t>
         </is>
       </c>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>Akitas</t>
+          <t>SUXIANGVAC</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Akitas/page/BE01E01C-FB27-4053-9F09-4CEDBCF3376A?lp_asin=B0FH4QN7S1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=SUXIANGVAC</t>
         </is>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>Akitas U10 Cordless Vacuum Cleaner – 2-in-1 Stick &amp; Handheld Design with Auto-Charging Docking station, Lightweight 2.4kg, Fo</t>
+          <t>SUXIANGVAC Cordless Vacuum Cleaner, 45Pa Suction/500W Motor/45Min Runtime - Cordless Rechargeable Vacuum with 73cm Extendable</t>
         </is>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FH4QN7S1?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FT7BQ1P4?psc=1</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61iXQi6Bc8L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81q6iYg2xZL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>B0FH4QN7S1</t>
+          <t>B0FT7BQ1P4</t>
         </is>
       </c>
       <c r="M45" s="14" t="inlineStr">
@@ -17786,13 +17752,13 @@
         </is>
       </c>
       <c r="O45" s="15">
-        <v>6487</v>
+        <v>11282</v>
       </c>
       <c r="P45" s="15">
-        <v>1932</v>
+        <v>5254</v>
       </c>
       <c r="Q45" s="16">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="R45" s="17" t="inlineStr">
         <is>
@@ -17801,63 +17767,61 @@
       </c>
       <c r="S45" s="18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>34</t>
         </is>
       </c>
       <c r="T45" s="15">
-        <v>368</v>
+        <v>267</v>
       </c>
       <c r="U45" s="16">
-        <v>-0.81</v>
+        <v>0.01</v>
       </c>
       <c r="V45" s="15">
-        <v>24284</v>
+        <v>19488</v>
       </c>
       <c r="W45" s="15" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="X45" s="15">
-        <v>12300</v>
+        <v>7850</v>
       </c>
       <c r="Y45" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z45" s="20">
-        <v>65.99</v>
+        <v>72.99</v>
       </c>
       <c r="AA45"/>
       <c r="AB45"/>
-      <c r="AC45" s="2">
-        <v>20</v>
-      </c>
+      <c r="AC45" s="2"/>
       <c r="AD45" s="19">
-        <v>557</v>
+        <v>435</v>
       </c>
       <c r="AE45" s="15">
-        <v>397</v>
+        <v>3</v>
       </c>
       <c r="AF45" s="21">
         <v>4.4</v>
       </c>
       <c r="AG45" s="22">
-        <v>0</v>
+        <v>0.011200000000000002</v>
       </c>
       <c r="AH45" s="20">
-        <v>5.43</v>
+        <v>3.71</v>
       </c>
       <c r="AI45" s="16">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="AJ45"/>
       <c r="AK45" s="13" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="AL45" s="19">
-        <v>388</v>
+        <v>302</v>
       </c>
       <c r="AM45" s="13" t="inlineStr">
         <is>
@@ -17875,7 +17839,7 @@
       </c>
       <c r="AS45" s="14" t="inlineStr">
         <is>
-          <t>Chelsea &amp; Co</t>
+          <t>SuXiangVac UK</t>
         </is>
       </c>
       <c r="AT45" s="13" t="inlineStr">
@@ -17890,12 +17854,12 @@
       </c>
       <c r="AV45" s="14" t="inlineStr">
         <is>
-          <t>Tin Hau Hong Kong 852 HK</t>
+          <t>新蒲崗 九龍 999077 HK</t>
         </is>
       </c>
       <c r="AW45" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A30X0O348OEO2T</t>
         </is>
       </c>
       <c r="AX45" s="13"/>
@@ -17912,7 +17876,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD45" s="13"/>
+      <c r="BD45" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE45" s="13"/>
       <c r="BF45" s="13"/>
       <c r="BG45" s="13"/>
@@ -17924,47 +17892,47 @@
       </c>
       <c r="BJ45" s="23" t="inlineStr">
         <is>
-          <t>2.15 kg</t>
+          <t>3.18 kg</t>
         </is>
       </c>
       <c r="BK45" s="23" t="inlineStr">
         <is>
-          <t>2.15 kg</t>
+          <t>3.18 kg</t>
         </is>
       </c>
       <c r="BL45" s="23" t="inlineStr">
         <is>
-          <t>28 x 24 x 100 cm</t>
+          <t>44 x 26 x 18 cm</t>
         </is>
       </c>
       <c r="BM45" s="23" t="inlineStr">
         <is>
-          <t>28.00 x 24.00 x 100.00 cm</t>
+          <t>44.00 x 26.00 x 18.00 cm</t>
         </is>
       </c>
       <c r="BN45" s="23" t="inlineStr">
         <is>
-          <t>3.43 kg</t>
+          <t>3.49 kg</t>
         </is>
       </c>
       <c r="BO45" s="23" t="inlineStr">
         <is>
-          <t>3.43 kg</t>
+          <t>3.49 kg</t>
         </is>
       </c>
       <c r="BP45" s="23" t="inlineStr">
         <is>
-          <t>56.6 x 25.7 x 22 cm</t>
+          <t>44.3 x 30.7 x 18.4 cm</t>
         </is>
       </c>
       <c r="BQ45" s="23" t="inlineStr">
         <is>
-          <t>56.60 x 25.70 x 22.00 cm</t>
+          <t>44.30 x 30.70 x 18.40 cm</t>
         </is>
       </c>
       <c r="BR45" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -17975,40 +17943,40 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0FT7BQ1P4</t>
+          <t>B0HF818ZJD</t>
         </is>
       </c>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>SUXIANGVAC</t>
+          <t>Honiture Clean</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=SUXIANGVAC</t>
+          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Honiture+Clean</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>SUXIANGVAC Cordless Vacuum Cleaner, 45Pa Suction/500W Motor/45Min Runtime - Cordless Rechargeable Vacuum with 73cm Extendable</t>
+          <t>Honiture Clean Cordless Vacuum Cleaner, 55KPa/650W Stick Vacuum, 60min Runtime, 90° Foldable Tube, Self-Standing Anti-Tangle</t>
         </is>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FT7BQ1P4?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0HF818ZJD?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81q6iYg2xZL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71p1cQ8K3nL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0FT7BQ1P4</t>
+          <t>B0HF818ZJD</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
@@ -18022,13 +17990,13 @@
         </is>
       </c>
       <c r="O46" s="15">
-        <v>11282</v>
+        <v>6908</v>
       </c>
       <c r="P46" s="15">
-        <v>5254</v>
+        <v>23216</v>
       </c>
       <c r="Q46" s="16">
-        <v>0.32</v>
+        <v>0.77</v>
       </c>
       <c r="R46" s="17" t="inlineStr">
         <is>
@@ -18037,46 +18005,44 @@
       </c>
       <c r="S46" s="18" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="T46" s="15">
-        <v>267</v>
-      </c>
-      <c r="U46" s="16">
-        <v>0.01</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="U46" s="16"/>
       <c r="V46" s="15">
-        <v>19488</v>
+        <v>16638</v>
       </c>
       <c r="W46" s="15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X46" s="15">
-        <v>7850</v>
+        <v>18682</v>
       </c>
       <c r="Y46" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z46" s="20">
-        <v>72.99</v>
+        <v>79.99</v>
       </c>
       <c r="AA46"/>
       <c r="AB46"/>
       <c r="AC46" s="2"/>
       <c r="AD46" s="19">
-        <v>435</v>
+        <v>12</v>
       </c>
       <c r="AE46" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF46" s="21">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AG46" s="22">
-        <v>0.011200000000000002</v>
+        <v>0.024</v>
       </c>
       <c r="AH46" s="20">
         <v>3.71</v>
@@ -18087,11 +18053,11 @@
       <c r="AJ46"/>
       <c r="AK46" s="13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="AL46" s="19">
-        <v>302</v>
+        <v>31</v>
       </c>
       <c r="AM46" s="13" t="inlineStr">
         <is>
@@ -18109,7 +18075,7 @@
       </c>
       <c r="AS46" s="14" t="inlineStr">
         <is>
-          <t>SuXiangVac UK</t>
+          <t>Skyuan</t>
         </is>
       </c>
       <c r="AT46" s="13" t="inlineStr">
@@ -18119,17 +18085,17 @@
       </c>
       <c r="AU46" s="13" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV46" s="14" t="inlineStr">
         <is>
-          <t>新蒲崗 九龍 999077 HK</t>
+          <t>深圳市 广东 518000 CN</t>
         </is>
       </c>
       <c r="AW46" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A30X0O348OEO2T</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AHXM9EXJUYAPG</t>
         </is>
       </c>
       <c r="AX46" s="13"/>
@@ -18162,42 +18128,42 @@
       </c>
       <c r="BJ46" s="23" t="inlineStr">
         <is>
-          <t>3.18 kg</t>
+          <t>2.36 kg</t>
         </is>
       </c>
       <c r="BK46" s="23" t="inlineStr">
         <is>
-          <t>3.18 kg</t>
+          <t>2.36 kg</t>
         </is>
       </c>
       <c r="BL46" s="23" t="inlineStr">
         <is>
-          <t>44 x 26 x 18 cm</t>
+          <t>40 x 29.5 x 19 cm</t>
         </is>
       </c>
       <c r="BM46" s="23" t="inlineStr">
         <is>
-          <t>44.00 x 26.00 x 18.00 cm</t>
+          <t>40.00 x 29.50 x 19.00 cm</t>
         </is>
       </c>
       <c r="BN46" s="23" t="inlineStr">
         <is>
-          <t>3.49 kg</t>
+          <t>3.64 kg</t>
         </is>
       </c>
       <c r="BO46" s="23" t="inlineStr">
         <is>
-          <t>3.49 kg</t>
+          <t>3.64 kg</t>
         </is>
       </c>
       <c r="BP46" s="23" t="inlineStr">
         <is>
-          <t>44.3 x 30.7 x 18.4 cm</t>
+          <t>43.1 x 30.6 x 19.4 cm</t>
         </is>
       </c>
       <c r="BQ46" s="23" t="inlineStr">
         <is>
-          <t>44.30 x 30.70 x 18.40 cm</t>
+          <t>43.10 x 30.60 x 19.40 cm</t>
         </is>
       </c>
       <c r="BR46" s="13" t="inlineStr">
@@ -18213,40 +18179,40 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B0HF818ZJD</t>
+          <t>B0FSF6XG22</t>
         </is>
       </c>
       <c r="D47" s="14"/>
       <c r="E47" s="14"/>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>Honiture Clean</t>
+          <t>Olsen &amp;amp; Smith</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Honiture+Clean</t>
+          <t>https://www.amazon.co.uk/stores/OlsenSmith/page/1FA1F547-221C-40C6-BA4F-6E13B39F7CE1?lp_asin=B0FSF6XG22&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>Honiture Clean Cordless Vacuum Cleaner, 55KPa/650W Stick Vacuum, 60min Runtime, 90° Foldable Tube, Self-Standing Anti-Tangle</t>
+          <t>Olsen &amp; Smith Self-Empty Cordless Vacuum Cleaner, 1.96kg Stick &amp; HandheldsLightweight Bagless Hoover, 18kPa Suction, 25min</t>
         </is>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0HF818ZJD?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FSF6XG22?psc=1</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71p1cQ8K3nL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41cxjopmqiL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>B0HF818ZJD</t>
+          <t>B0FSF6XG22</t>
         </is>
       </c>
       <c r="M47" s="14" t="inlineStr">
@@ -18260,13 +18226,13 @@
         </is>
       </c>
       <c r="O47" s="15">
-        <v>6908</v>
+        <v>24107</v>
       </c>
       <c r="P47" s="15">
-        <v>23216</v>
+        <v>-2182</v>
       </c>
       <c r="Q47" s="16">
-        <v>0.77</v>
+        <v>-0.1</v>
       </c>
       <c r="R47" s="17" t="inlineStr">
         <is>
@@ -18275,97 +18241,99 @@
       </c>
       <c r="S47" s="18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>56</t>
         </is>
       </c>
       <c r="T47" s="15">
-        <v>208</v>
-      </c>
-      <c r="U47" s="16"/>
+        <v>223</v>
+      </c>
+      <c r="U47" s="16">
+        <v>0.11</v>
+      </c>
       <c r="V47" s="15">
-        <v>16638</v>
+        <v>11148</v>
       </c>
       <c r="W47" s="15" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="X47" s="15">
-        <v>18682</v>
+        <v>4999</v>
       </c>
       <c r="Y47" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z47" s="20">
-        <v>79.99</v>
+        <v>49.99</v>
       </c>
       <c r="AA47"/>
       <c r="AB47"/>
       <c r="AC47" s="2"/>
       <c r="AD47" s="19">
-        <v>12</v>
+        <v>123</v>
       </c>
       <c r="AE47" s="15">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AF47" s="21">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="AG47" s="22">
-        <v>0.024</v>
+        <v>0.0762</v>
       </c>
       <c r="AH47" s="20">
-        <v>3.71</v>
+        <v>6.04</v>
       </c>
       <c r="AI47" s="16">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AJ47"/>
       <c r="AK47" s="13" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AL47" s="19">
-        <v>31</v>
+        <v>361</v>
       </c>
       <c r="AM47" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN47" s="13"/>
       <c r="AO47" s="13"/>
       <c r="AP47"/>
       <c r="AQ47" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR47" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS47" s="14" t="inlineStr">
         <is>
-          <t>Skyuan</t>
+          <t>Packed Direct</t>
         </is>
       </c>
       <c r="AT47" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU47" s="13" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="AV47" s="14" t="inlineStr">
         <is>
-          <t>深圳市 广东 518000 CN</t>
+          <t>Basildon SS156TF GB</t>
         </is>
       </c>
       <c r="AW47" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AHXM9EXJUYAPG</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3DJDH6QTTYBC6</t>
         </is>
       </c>
       <c r="AX47" s="13"/>
@@ -18398,47 +18366,43 @@
       </c>
       <c r="BJ47" s="23" t="inlineStr">
         <is>
-          <t>2.36 kg</t>
+          <t>5.4 kg</t>
         </is>
       </c>
       <c r="BK47" s="23" t="inlineStr">
         <is>
-          <t>2.36 kg</t>
+          <t>5.40 kg</t>
         </is>
       </c>
       <c r="BL47" s="23" t="inlineStr">
         <is>
-          <t>40 x 29.5 x 19 cm</t>
-        </is>
-      </c>
-      <c r="BM47" s="23" t="inlineStr">
-        <is>
-          <t>40.00 x 29.50 x 19.00 cm</t>
-        </is>
-      </c>
+          <t>27L x 27W x 127H centimetres</t>
+        </is>
+      </c>
+      <c r="BM47" s="23"/>
       <c r="BN47" s="23" t="inlineStr">
         <is>
-          <t>3.64 kg</t>
+          <t>8.5 kg</t>
         </is>
       </c>
       <c r="BO47" s="23" t="inlineStr">
         <is>
-          <t>3.64 kg</t>
+          <t>8.50 kg</t>
         </is>
       </c>
       <c r="BP47" s="23" t="inlineStr">
         <is>
-          <t>43.1 x 30.6 x 19.4 cm</t>
+          <t>73.2 x 41.4 x 17.6 cm</t>
         </is>
       </c>
       <c r="BQ47" s="23" t="inlineStr">
         <is>
-          <t>43.10 x 30.60 x 19.40 cm</t>
+          <t>73.20 x 41.40 x 17.60 cm</t>
         </is>
       </c>
       <c r="BR47" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -18449,40 +18413,40 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B0FSF6XG22</t>
+          <t>B0C37SVX2V</t>
         </is>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>Olsen &amp;amp; Smith</t>
+          <t>Duronic</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/OlsenSmith/page/1FA1F547-221C-40C6-BA4F-6E13B39F7CE1?lp_asin=B0FSF6XG22&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/Duronic/page/A5A8FDD3-4203-4BE8-BCF2-850400F720CD?lp_asin=B0C37SVX2V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Olsen &amp; Smith Self-Empty Cordless Vacuum Cleaner, 1.96kg Stick &amp; HandheldsLightweight Bagless Hoover, 18kPa Suction, 25min</t>
+          <t>Duronic Cordless Vacuum Cleaner VC24 Rechargeable Upright Handheld Stick Cleaners, Bagless Powerful Hand Held Hoover for Floo</t>
         </is>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FSF6XG22?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0C37SVX2V?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41cxjopmqiL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51+CY4t2PIL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B0FSF6XG22</t>
+          <t>B0C37SVX2V</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
@@ -18496,13 +18460,13 @@
         </is>
       </c>
       <c r="O48" s="15">
-        <v>24107</v>
+        <v>10784</v>
       </c>
       <c r="P48" s="15">
-        <v>-2182</v>
+        <v>4528</v>
       </c>
       <c r="Q48" s="16">
-        <v>-0.1</v>
+        <v>0.31</v>
       </c>
       <c r="R48" s="17" t="inlineStr">
         <is>
@@ -18511,84 +18475,86 @@
       </c>
       <c r="S48" s="18" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T48" s="15">
-        <v>223</v>
+        <v>260</v>
       </c>
       <c r="U48" s="16">
-        <v>0.11</v>
+        <v>0.47</v>
       </c>
       <c r="V48" s="15">
-        <v>11148</v>
+        <v>11047</v>
       </c>
       <c r="W48" s="15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="X48" s="15">
-        <v>4999</v>
+        <v>2125</v>
       </c>
       <c r="Y48" s="19">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z48" s="20">
         <v>49.99</v>
       </c>
       <c r="AA48"/>
       <c r="AB48"/>
-      <c r="AC48" s="2"/>
+      <c r="AC48" s="2">
+        <v>127</v>
+      </c>
       <c r="AD48" s="19">
-        <v>123</v>
+        <v>75</v>
       </c>
       <c r="AE48" s="15">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AF48" s="21">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AG48" s="22">
-        <v>0.0762</v>
+        <v>0</v>
       </c>
       <c r="AH48" s="20">
-        <v>6.04</v>
+        <v>5.28</v>
       </c>
       <c r="AI48" s="16">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="AJ48"/>
       <c r="AK48" s="13" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-05-29</t>
         </is>
       </c>
       <c r="AL48" s="19">
-        <v>361</v>
+        <v>1213</v>
       </c>
       <c r="AM48" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN48" s="13"/>
       <c r="AO48" s="13"/>
       <c r="AP48"/>
       <c r="AQ48" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR48" s="19">
         <v>3</v>
       </c>
       <c r="AS48" s="14" t="inlineStr">
         <is>
-          <t>Packed Direct</t>
+          <t>DURONIC</t>
         </is>
       </c>
       <c r="AT48" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AU48" s="13" t="inlineStr">
@@ -18598,12 +18564,12 @@
       </c>
       <c r="AV48" s="14" t="inlineStr">
         <is>
-          <t>Basildon SS156TF GB</t>
+          <t>ROMFORD Essex RM3 8SB GB</t>
         </is>
       </c>
       <c r="AW48" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3DJDH6QTTYBC6</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=APLJ5AXPSKRV0</t>
         </is>
       </c>
       <c r="AX48" s="13"/>
@@ -18636,38 +18602,38 @@
       </c>
       <c r="BJ48" s="23" t="inlineStr">
         <is>
-          <t>5.4 kg</t>
+          <t>2.9 kg</t>
         </is>
       </c>
       <c r="BK48" s="23" t="inlineStr">
         <is>
-          <t>5.40 kg</t>
+          <t>2.90 kg</t>
         </is>
       </c>
       <c r="BL48" s="23" t="inlineStr">
         <is>
-          <t>27L x 27W x 127H centimetres</t>
+          <t>25L x 34W x 93H centimetres</t>
         </is>
       </c>
       <c r="BM48" s="23"/>
       <c r="BN48" s="23" t="inlineStr">
         <is>
-          <t>8.5 kg</t>
+          <t>3.38 kg</t>
         </is>
       </c>
       <c r="BO48" s="23" t="inlineStr">
         <is>
-          <t>8.50 kg</t>
+          <t>3.38 kg</t>
         </is>
       </c>
       <c r="BP48" s="23" t="inlineStr">
         <is>
-          <t>73.2 x 41.4 x 17.6 cm</t>
+          <t>45.2 x 28.6 x 19.7 cm</t>
         </is>
       </c>
       <c r="BQ48" s="23" t="inlineStr">
         <is>
-          <t>73.20 x 41.40 x 17.60 cm</t>
+          <t>45.20 x 28.60 x 19.70 cm</t>
         </is>
       </c>
       <c r="BR48" s="13" t="inlineStr">
@@ -18683,40 +18649,40 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B0C37SVX2V</t>
+          <t>B0FGPM83WQ</t>
         </is>
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="14"/>
       <c r="F49" s="14" t="inlineStr">
         <is>
-          <t>Duronic</t>
+          <t>Vlihapy</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Duronic/page/A5A8FDD3-4203-4BE8-BCF2-850400F720CD?lp_asin=B0C37SVX2V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Vlihapy</t>
         </is>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>Duronic Cordless Vacuum Cleaner VC24 Rechargeable Upright Handheld Stick Cleaners, Bagless Powerful Hand Held Hoover for Floo</t>
+          <t>6 IN 1 Cordless Vacuum Cleaner 160W 15000PA Powerful Stick Vacuums &amp; Electric Brooms with LED, 3000mAh Rechargeable Battery,</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0C37SVX2V?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FGPM83WQ?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51+CY4t2PIL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61YPwkc2MmL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B0C37SVX2V</t>
+          <t>B0FGPM83WQ</t>
         </is>
       </c>
       <c r="M49" s="14" t="inlineStr">
@@ -18730,13 +18696,13 @@
         </is>
       </c>
       <c r="O49" s="15">
-        <v>10784</v>
+        <v>12312</v>
       </c>
       <c r="P49" s="15">
-        <v>4528</v>
+        <v>-2015</v>
       </c>
       <c r="Q49" s="16">
-        <v>0.31</v>
+        <v>-0.2</v>
       </c>
       <c r="R49" s="17" t="inlineStr">
         <is>
@@ -18749,59 +18715,55 @@
         </is>
       </c>
       <c r="T49" s="15">
-        <v>260</v>
+        <v>337</v>
       </c>
       <c r="U49" s="16">
         <v>0.47</v>
       </c>
       <c r="V49" s="15">
-        <v>11047</v>
+        <v>10777</v>
       </c>
       <c r="W49" s="15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>300</t>
         </is>
       </c>
       <c r="X49" s="15">
-        <v>2125</v>
+        <v>12891</v>
       </c>
       <c r="Y49" s="19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z49" s="20">
-        <v>49.99</v>
+        <v>42.97</v>
       </c>
       <c r="AA49"/>
       <c r="AB49"/>
-      <c r="AC49" s="2">
-        <v>127</v>
-      </c>
+      <c r="AC49" s="2"/>
       <c r="AD49" s="19">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="AE49" s="15">
+        <v>12</v>
+      </c>
+      <c r="AF49" s="21">
+        <v>4.5</v>
+      </c>
+      <c r="AG49" s="22">
+        <v>0.0356</v>
+      </c>
+      <c r="AH49" s="20"/>
+      <c r="AI49" s="16">
         <v>0</v>
-      </c>
-      <c r="AF49" s="21">
-        <v>3.8</v>
-      </c>
-      <c r="AG49" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH49" s="20">
-        <v>5.28</v>
-      </c>
-      <c r="AI49" s="16">
-        <v>0.88</v>
       </c>
       <c r="AJ49"/>
       <c r="AK49" s="13" t="inlineStr">
         <is>
-          <t>2023-05-29</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AL49" s="19">
-        <v>1213</v>
+        <v>438</v>
       </c>
       <c r="AM49" s="13" t="inlineStr">
         <is>
@@ -18812,14 +18774,14 @@
       <c r="AO49" s="13"/>
       <c r="AP49"/>
       <c r="AQ49" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR49" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS49" s="14" t="inlineStr">
         <is>
-          <t>DURONIC</t>
+          <t>Treasuretool</t>
         </is>
       </c>
       <c r="AT49" s="13" t="inlineStr">
@@ -18829,17 +18791,17 @@
       </c>
       <c r="AU49" s="13" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV49" s="14" t="inlineStr">
         <is>
-          <t>ROMFORD Essex RM3 8SB GB</t>
+          <t>南通市 崇川区 江苏省 226014 CN</t>
         </is>
       </c>
       <c r="AW49" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=APLJ5AXPSKRV0</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KUVQEB99D827</t>
         </is>
       </c>
       <c r="AX49" s="13"/>
@@ -18851,11 +18813,7 @@
       <c r="AZ49" s="13"/>
       <c r="BA49" s="13"/>
       <c r="BB49" s="13"/>
-      <c r="BC49" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC49" s="13"/>
       <c r="BD49" s="13" t="inlineStr">
         <is>
           <t>Y</t>
@@ -18870,47 +18828,23 @@
           <t>Amazon's Choice</t>
         </is>
       </c>
-      <c r="BJ49" s="23" t="inlineStr">
-        <is>
-          <t>2.9 kg</t>
-        </is>
-      </c>
-      <c r="BK49" s="23" t="inlineStr">
-        <is>
-          <t>2.90 kg</t>
-        </is>
-      </c>
+      <c r="BJ49" s="23"/>
+      <c r="BK49" s="23"/>
       <c r="BL49" s="23" t="inlineStr">
         <is>
-          <t>25L x 34W x 93H centimetres</t>
-        </is>
-      </c>
-      <c r="BM49" s="23"/>
-      <c r="BN49" s="23" t="inlineStr">
-        <is>
-          <t>3.38 kg</t>
-        </is>
-      </c>
-      <c r="BO49" s="23" t="inlineStr">
-        <is>
-          <t>3.38 kg</t>
-        </is>
-      </c>
-      <c r="BP49" s="23" t="inlineStr">
-        <is>
-          <t>45.2 x 28.6 x 19.7 cm</t>
-        </is>
-      </c>
-      <c r="BQ49" s="23" t="inlineStr">
-        <is>
-          <t>45.20 x 28.60 x 19.70 cm</t>
-        </is>
-      </c>
-      <c r="BR49" s="13" t="inlineStr">
-        <is>
-          <t>轻型标准大件</t>
-        </is>
-      </c>
+          <t>23.5 x 15 x 110 cm</t>
+        </is>
+      </c>
+      <c r="BM49" s="23" t="inlineStr">
+        <is>
+          <t>23.50 x 15.00 x 110.00 cm</t>
+        </is>
+      </c>
+      <c r="BN49" s="23"/>
+      <c r="BO49" s="23"/>
+      <c r="BP49" s="23"/>
+      <c r="BQ49" s="23"/>
+      <c r="BR49" s="13"/>
     </row>
     <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="13">
@@ -18919,40 +18853,40 @@
       <c r="B50" s="13"/>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>B0FGPM83WQ</t>
+          <t>B07ZQH4T3T</t>
         </is>
       </c>
       <c r="D50" s="14"/>
       <c r="E50" s="14"/>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>Vlihapy</t>
+          <t>JML</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Vlihapy</t>
+          <t>https://www.amazon.co.uk/stores/JML/page/7D82F081-93D9-4B24-9DE9-D18ADF17C695?lp_asin=B07ZQH4T3T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>6 IN 1 Cordless Vacuum Cleaner 160W 15000PA Powerful Stick Vacuums &amp; Electric Brooms with LED, 3000mAh Rechargeable Battery,</t>
+          <t>JML Swivel Sweeper Cordless Vacuum Cleaner – Rechargeable Floor Sweepers360 degree swivel head bends under furniture – ligh</t>
         </is>
       </c>
       <c r="I50" s="14"/>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FGPM83WQ?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B07ZQH4T3T?psc=1</t>
         </is>
       </c>
       <c r="K50" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61YPwkc2MmL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81IMjIncpDL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>B0FGPM83WQ</t>
+          <t>B07ZQH4T3T</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
@@ -18966,13 +18900,13 @@
         </is>
       </c>
       <c r="O50" s="15">
-        <v>12312</v>
+        <v>8959</v>
       </c>
       <c r="P50" s="15">
-        <v>-2015</v>
+        <v>3124</v>
       </c>
       <c r="Q50" s="16">
-        <v>-0.2</v>
+        <v>0.26</v>
       </c>
       <c r="R50" s="17" t="inlineStr">
         <is>
@@ -18981,17 +18915,17 @@
       </c>
       <c r="S50" s="18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T50" s="15">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="U50" s="16">
-        <v>0.47</v>
+        <v>0.54</v>
       </c>
       <c r="V50" s="15">
-        <v>10777</v>
+        <v>5321</v>
       </c>
       <c r="W50" s="15" t="inlineStr">
         <is>
@@ -18999,41 +18933,45 @@
         </is>
       </c>
       <c r="X50" s="15">
-        <v>12891</v>
+        <v>6273</v>
       </c>
       <c r="Y50" s="19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z50" s="20">
-        <v>42.97</v>
+        <v>14.99</v>
       </c>
       <c r="AA50"/>
       <c r="AB50"/>
-      <c r="AC50" s="2"/>
+      <c r="AC50" s="2">
+        <v>21</v>
+      </c>
       <c r="AD50" s="19">
-        <v>28</v>
+        <v>2414</v>
       </c>
       <c r="AE50" s="15">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AF50" s="21">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AG50" s="22">
-        <v>0.0356</v>
-      </c>
-      <c r="AH50" s="20"/>
+        <v>0.0113</v>
+      </c>
+      <c r="AH50" s="20">
+        <v>3.4</v>
+      </c>
       <c r="AI50" s="16">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="AJ50"/>
       <c r="AK50" s="13" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AL50" s="19">
-        <v>438</v>
+        <v>2169</v>
       </c>
       <c r="AM50" s="13" t="inlineStr">
         <is>
@@ -19044,14 +18982,14 @@
       <c r="AO50" s="13"/>
       <c r="AP50"/>
       <c r="AQ50" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR50" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS50" s="14" t="inlineStr">
         <is>
-          <t>Treasuretool</t>
+          <t>JML Direct</t>
         </is>
       </c>
       <c r="AT50" s="13" t="inlineStr">
@@ -19061,17 +18999,17 @@
       </c>
       <c r="AU50" s="13" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="AV50" s="14" t="inlineStr">
         <is>
-          <t>南通市 崇川区 江苏省 226014 CN</t>
+          <t>London London W4 5RU GB</t>
         </is>
       </c>
       <c r="AW50" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KUVQEB99D827</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KNWE4UE7YTH1</t>
         </is>
       </c>
       <c r="AX50" s="13"/>
@@ -19083,7 +19021,11 @@
       <c r="AZ50" s="13"/>
       <c r="BA50" s="13"/>
       <c r="BB50" s="13"/>
-      <c r="BC50" s="13"/>
+      <c r="BC50" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD50" s="13" t="inlineStr">
         <is>
           <t>Y</t>
@@ -19098,259 +19040,47 @@
           <t>Amazon's Choice</t>
         </is>
       </c>
-      <c r="BJ50" s="23"/>
-      <c r="BK50" s="23"/>
+      <c r="BJ50" s="23" t="inlineStr">
+        <is>
+          <t>907 g</t>
+        </is>
+      </c>
+      <c r="BK50" s="23" t="inlineStr">
+        <is>
+          <t>907.00 g</t>
+        </is>
+      </c>
       <c r="BL50" s="23" t="inlineStr">
         <is>
-          <t>23.5 x 15 x 110 cm</t>
+          <t>20 x 18 x 7 cm</t>
         </is>
       </c>
       <c r="BM50" s="23" t="inlineStr">
         <is>
-          <t>23.50 x 15.00 x 110.00 cm</t>
-        </is>
-      </c>
-      <c r="BN50" s="23"/>
-      <c r="BO50" s="23"/>
-      <c r="BP50" s="23"/>
-      <c r="BQ50" s="23"/>
-      <c r="BR50" s="13"/>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B07ZQH4T3T</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14" t="inlineStr">
-        <is>
-          <t>JML</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/stores/JML/page/7D82F081-93D9-4B24-9DE9-D18ADF17C695?lp_asin=B07ZQH4T3T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>JML Swivel Sweeper Cordless Vacuum Cleaner – Rechargeable Floor Sweepers360 degree swivel head bends under furniture – ligh</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B07ZQH4T3T?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81IMjIncpDL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B07ZQH4T3T</t>
-        </is>
-      </c>
-      <c r="M51" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen:Kitchen &amp; Home Appliances:Vacuums &amp; Floor Care:Vacuums:Stick Vacuums &amp; Electric Brooms</t>
-        </is>
-      </c>
-      <c r="N51" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen</t>
-        </is>
-      </c>
-      <c r="O51" s="15">
-        <v>8959</v>
-      </c>
-      <c r="P51" s="15">
-        <v>3124</v>
-      </c>
-      <c r="Q51" s="16">
-        <v>0.26</v>
-      </c>
-      <c r="R51" s="17" t="inlineStr">
-        <is>
-          <t>Stick Vacuums &amp; Electric Brooms</t>
-        </is>
-      </c>
-      <c r="S51" s="18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="T51" s="15">
-        <v>355</v>
-      </c>
-      <c r="U51" s="16">
-        <v>0.54</v>
-      </c>
-      <c r="V51" s="15">
-        <v>5321</v>
-      </c>
-      <c r="W51" s="15" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="X51" s="15">
-        <v>6273</v>
-      </c>
-      <c r="Y51" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z51" s="20">
-        <v>14.99</v>
-      </c>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD51" s="19">
-        <v>2414</v>
-      </c>
-      <c r="AE51" s="15">
-        <v>4</v>
-      </c>
-      <c r="AF51" s="21">
-        <v>4</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0.0113</v>
-      </c>
-      <c r="AH51" s="20">
-        <v>3.4</v>
-      </c>
-      <c r="AI51" s="16">
-        <v>0.77</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="13" t="inlineStr">
-        <is>
-          <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AL51" s="19">
-        <v>2169</v>
-      </c>
-      <c r="AM51" s="13" t="inlineStr">
-        <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR51" s="19">
-        <v>2</v>
-      </c>
-      <c r="AS51" s="14" t="inlineStr">
-        <is>
-          <t>JML Direct</t>
-        </is>
-      </c>
-      <c r="AT51" s="13" t="inlineStr">
-        <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AU51" s="13" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="AV51" s="14" t="inlineStr">
-        <is>
-          <t>London London W4 5RU GB</t>
-        </is>
-      </c>
-      <c r="AW51" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KNWE4UE7YTH1</t>
-        </is>
-      </c>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
-      <c r="BJ51" s="23" t="inlineStr">
-        <is>
-          <t>907 g</t>
-        </is>
-      </c>
-      <c r="BK51" s="23" t="inlineStr">
-        <is>
-          <t>907.00 g</t>
-        </is>
-      </c>
-      <c r="BL51" s="23" t="inlineStr">
-        <is>
-          <t>20 x 18 x 7 cm</t>
-        </is>
-      </c>
-      <c r="BM51" s="23" t="inlineStr">
-        <is>
           <t>20.00 x 18.00 x 7.00 cm</t>
         </is>
       </c>
-      <c r="BN51" s="23" t="inlineStr">
+      <c r="BN50" s="23" t="inlineStr">
         <is>
           <t>1.31 kg</t>
         </is>
       </c>
-      <c r="BO51" s="23" t="inlineStr">
+      <c r="BO50" s="23" t="inlineStr">
         <is>
           <t>1.31 kg</t>
         </is>
       </c>
-      <c r="BP51" s="23" t="inlineStr">
+      <c r="BP50" s="23" t="inlineStr">
         <is>
           <t>39.3 x 23.8 x 7.9 cm</t>
         </is>
       </c>
-      <c r="BQ51" s="23" t="inlineStr">
+      <c r="BQ50" s="23" t="inlineStr">
         <is>
           <t>39.30 x 23.80 x 7.90 cm</t>
         </is>
       </c>
-      <c r="BR51" s="13" t="inlineStr">
+      <c r="BR50" s="13" t="inlineStr">
         <is>
           <t>标准包裹</t>
         </is>
@@ -19628,117 +19358,110 @@
     <hyperlink ref="M37" r:id="rId266" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
     <hyperlink ref="N37" r:id="rId267"/>
     <hyperlink ref="AW37" r:id="rId268" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1AFJESMA8SCN6"/>
-    <hyperlink ref="C38" r:id="rId269" tooltip="https://www.amazon.co.uk/dp/B0F9YPP9C3"/>
-    <hyperlink ref="G38" r:id="rId270" tooltip="https://www.amazon.co.uk/stores/Shark/page/525766F4-D5DD-4FFC-8A20-92AC184FF87C?lp_asin=B0F9YPP9C3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J38" r:id="rId271" tooltip="https://www.amazon.co.uk/dp/B0F9YPP9C3?psc=1"/>
-    <hyperlink ref="K38" r:id="rId272" tooltip="https://images-na.ssl-images-amazon.com/images/I/61y78uO9VYL._AC_US600_.jpg"/>
-    <hyperlink ref="L38" r:id="rId273" tooltip="https://www.amazon.co.uk/dp/B0F9YPP9C3"/>
+    <hyperlink ref="C38" r:id="rId269" tooltip="https://www.amazon.co.uk/dp/B0GVY4FWDK"/>
+    <hyperlink ref="G38" r:id="rId270" tooltip="https://www.amazon.co.uk/stores/INTETURE/page/81A67A11-BDF9-40C2-8A10-6B3828AADF13?lp_asin=B0GVY4FWDK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J38" r:id="rId271" tooltip="https://www.amazon.co.uk/dp/B0GVY4FWDK?psc=1"/>
+    <hyperlink ref="K38" r:id="rId272" tooltip="https://images-na.ssl-images-amazon.com/images/I/81amekLcGTL._AC_US600_.jpg"/>
+    <hyperlink ref="L38" r:id="rId273" tooltip="https://www.amazon.co.uk/dp/B0GVY4FWDK"/>
     <hyperlink ref="M38" r:id="rId274" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
     <hyperlink ref="N38" r:id="rId275"/>
-    <hyperlink ref="C39" r:id="rId276" tooltip="https://www.amazon.co.uk/dp/B0GVY4FWDK"/>
-    <hyperlink ref="G39" r:id="rId277" tooltip="https://www.amazon.co.uk/stores/INTETURE/page/81A67A11-BDF9-40C2-8A10-6B3828AADF13?lp_asin=B0GVY4FWDK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J39" r:id="rId278" tooltip="https://www.amazon.co.uk/dp/B0GVY4FWDK?psc=1"/>
-    <hyperlink ref="K39" r:id="rId279" tooltip="https://images-na.ssl-images-amazon.com/images/I/81amekLcGTL._AC_US600_.jpg"/>
-    <hyperlink ref="L39" r:id="rId280" tooltip="https://www.amazon.co.uk/dp/B0GVY4FWDK"/>
-    <hyperlink ref="M39" r:id="rId281" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N39" r:id="rId282"/>
-    <hyperlink ref="AW39" r:id="rId283" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3TL6V3PPJTQHJ"/>
-    <hyperlink ref="C40" r:id="rId284" tooltip="https://www.amazon.co.uk/dp/B0H1BHBKTC"/>
-    <hyperlink ref="G40" r:id="rId285" tooltip="https://www.amazon.co.uk/stores/SMOTURE/page/C0B880AC-DBCF-4263-BE20-34B07DB6DBA9?lp_asin=B0H1BHBKTC&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J40" r:id="rId286" tooltip="https://www.amazon.co.uk/dp/B0H1BHBKTC?psc=1"/>
-    <hyperlink ref="K40" r:id="rId287" tooltip="https://images-na.ssl-images-amazon.com/images/I/81zaCtkHd-L._AC_US600_.jpg"/>
-    <hyperlink ref="L40" r:id="rId288" tooltip="https://www.amazon.co.uk/dp/B0H1BHBKTC"/>
-    <hyperlink ref="M40" r:id="rId289" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N40" r:id="rId290"/>
-    <hyperlink ref="AW40" r:id="rId291" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AN9MVBN9OI7JL"/>
-    <hyperlink ref="C41" r:id="rId292" tooltip="https://www.amazon.co.uk/dp/B0H1WC1PJ1"/>
-    <hyperlink ref="G41" r:id="rId293" tooltip="https://www.amazon.co.uk/stores/PROSCENIC/page/9D6AA08D-8BCB-40F7-A698-933D705EEDDF?lp_asin=B0H1WC1PJ1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J41" r:id="rId294" tooltip="https://www.amazon.co.uk/dp/B0H1WC1PJ1?psc=1"/>
-    <hyperlink ref="K41" r:id="rId295" tooltip="https://images-na.ssl-images-amazon.com/images/I/61xgSdYZzpL._AC_US600_.jpg"/>
-    <hyperlink ref="L41" r:id="rId296" tooltip="https://www.amazon.co.uk/dp/B0H1WC1PJ1"/>
+    <hyperlink ref="AW38" r:id="rId276" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3TL6V3PPJTQHJ"/>
+    <hyperlink ref="C39" r:id="rId277" tooltip="https://www.amazon.co.uk/dp/B0H1BHBKTC"/>
+    <hyperlink ref="G39" r:id="rId278" tooltip="https://www.amazon.co.uk/stores/SMOTURE/page/C0B880AC-DBCF-4263-BE20-34B07DB6DBA9?lp_asin=B0H1BHBKTC&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J39" r:id="rId279" tooltip="https://www.amazon.co.uk/dp/B0H1BHBKTC?psc=1"/>
+    <hyperlink ref="K39" r:id="rId280" tooltip="https://images-na.ssl-images-amazon.com/images/I/81zaCtkHd-L._AC_US600_.jpg"/>
+    <hyperlink ref="L39" r:id="rId281" tooltip="https://www.amazon.co.uk/dp/B0H1BHBKTC"/>
+    <hyperlink ref="M39" r:id="rId282" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N39" r:id="rId283"/>
+    <hyperlink ref="AW39" r:id="rId284" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AN9MVBN9OI7JL"/>
+    <hyperlink ref="C40" r:id="rId285" tooltip="https://www.amazon.co.uk/dp/B0H1WC1PJ1"/>
+    <hyperlink ref="G40" r:id="rId286" tooltip="https://www.amazon.co.uk/stores/PROSCENIC/page/9D6AA08D-8BCB-40F7-A698-933D705EEDDF?lp_asin=B0H1WC1PJ1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J40" r:id="rId287" tooltip="https://www.amazon.co.uk/dp/B0H1WC1PJ1?psc=1"/>
+    <hyperlink ref="K40" r:id="rId288" tooltip="https://images-na.ssl-images-amazon.com/images/I/61xgSdYZzpL._AC_US600_.jpg"/>
+    <hyperlink ref="L40" r:id="rId289" tooltip="https://www.amazon.co.uk/dp/B0H1WC1PJ1"/>
+    <hyperlink ref="M40" r:id="rId290" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N40" r:id="rId291"/>
+    <hyperlink ref="C41" r:id="rId292" tooltip="https://www.amazon.co.uk/dp/B09RMQ1XLL"/>
+    <hyperlink ref="G41" r:id="rId293" tooltip="https://www.amazon.co.uk/stores/VYTRONIX/page/0488BBB4-7668-4BD9-83CC-3C85540B802C?lp_asin=B09RMQ1XLL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J41" r:id="rId294" tooltip="https://www.amazon.co.uk/dp/B09RMQ1XLL?psc=1"/>
+    <hyperlink ref="K41" r:id="rId295" tooltip="https://images-na.ssl-images-amazon.com/images/I/51QJB9vzthL._AC_US600_.jpg"/>
+    <hyperlink ref="L41" r:id="rId296" tooltip="https://www.amazon.co.uk/dp/B09RMQ1XLL"/>
     <hyperlink ref="M41" r:id="rId297" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
     <hyperlink ref="N41" r:id="rId298"/>
-    <hyperlink ref="C42" r:id="rId299" tooltip="https://www.amazon.co.uk/dp/B09RMQ1XLL"/>
-    <hyperlink ref="G42" r:id="rId300" tooltip="https://www.amazon.co.uk/stores/VYTRONIX/page/0488BBB4-7668-4BD9-83CC-3C85540B802C?lp_asin=B09RMQ1XLL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J42" r:id="rId301" tooltip="https://www.amazon.co.uk/dp/B09RMQ1XLL?psc=1"/>
-    <hyperlink ref="K42" r:id="rId302" tooltip="https://images-na.ssl-images-amazon.com/images/I/51QJB9vzthL._AC_US600_.jpg"/>
-    <hyperlink ref="L42" r:id="rId303" tooltip="https://www.amazon.co.uk/dp/B09RMQ1XLL"/>
-    <hyperlink ref="M42" r:id="rId304" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N42" r:id="rId305"/>
-    <hyperlink ref="AW42" r:id="rId306" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZNUHI65TJJP2"/>
-    <hyperlink ref="C43" r:id="rId307" tooltip="https://www.amazon.co.uk/dp/B0H2J8QH51"/>
-    <hyperlink ref="G43" r:id="rId308" tooltip="https://www.amazon.co.uk/stores/VACTechPro/page/A2AA5919-757D-4EB7-AE3F-8644C68C4115?lp_asin=B0H2J8QH51&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J43" r:id="rId309" tooltip="https://www.amazon.co.uk/dp/B0H2J8QH51?psc=1"/>
-    <hyperlink ref="K43" r:id="rId310" tooltip="https://m.media-amazon.com/images/I/41LbZ7ZgbSL._AC_US600_.jpg"/>
-    <hyperlink ref="L43" r:id="rId311" tooltip="https://www.amazon.co.uk/dp/B0H2J8QH51"/>
-    <hyperlink ref="M43" r:id="rId312" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N43" r:id="rId313"/>
-    <hyperlink ref="AW43" r:id="rId314" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A14OQRLFZKKYSN"/>
-    <hyperlink ref="C44" r:id="rId315" tooltip="https://www.amazon.co.uk/dp/B0G1YQ9T93"/>
-    <hyperlink ref="G44" r:id="rId316" tooltip="https://www.amazon.co.uk/stores/Levoit/page/774A68E1-06B2-417A-85EE-3C62CCE4C91C?lp_asin=B0G1YQ9T93&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J44" r:id="rId317" tooltip="https://www.amazon.co.uk/dp/B0G1YQ9T93?psc=1"/>
-    <hyperlink ref="K44" r:id="rId318" tooltip="https://images-na.ssl-images-amazon.com/images/I/61GsdjWeYnL._AC_US600_.jpg"/>
-    <hyperlink ref="L44" r:id="rId319" tooltip="https://www.amazon.co.uk/dp/B0G1YQ9T93"/>
+    <hyperlink ref="AW41" r:id="rId299" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZNUHI65TJJP2"/>
+    <hyperlink ref="C42" r:id="rId300" tooltip="https://www.amazon.co.uk/dp/B0H2J8QH51"/>
+    <hyperlink ref="G42" r:id="rId301" tooltip="https://www.amazon.co.uk/stores/VACTechPro/page/A2AA5919-757D-4EB7-AE3F-8644C68C4115?lp_asin=B0H2J8QH51&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J42" r:id="rId302" tooltip="https://www.amazon.co.uk/dp/B0H2J8QH51?psc=1"/>
+    <hyperlink ref="K42" r:id="rId303" tooltip="https://m.media-amazon.com/images/I/41LbZ7ZgbSL._AC_US600_.jpg"/>
+    <hyperlink ref="L42" r:id="rId304" tooltip="https://www.amazon.co.uk/dp/B0H2J8QH51"/>
+    <hyperlink ref="M42" r:id="rId305" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N42" r:id="rId306"/>
+    <hyperlink ref="AW42" r:id="rId307" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A14OQRLFZKKYSN"/>
+    <hyperlink ref="C43" r:id="rId308" tooltip="https://www.amazon.co.uk/dp/B0G1YQ9T93"/>
+    <hyperlink ref="G43" r:id="rId309" tooltip="https://www.amazon.co.uk/stores/Levoit/page/774A68E1-06B2-417A-85EE-3C62CCE4C91C?lp_asin=B0G1YQ9T93&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J43" r:id="rId310" tooltip="https://www.amazon.co.uk/dp/B0G1YQ9T93?psc=1"/>
+    <hyperlink ref="K43" r:id="rId311" tooltip="https://images-na.ssl-images-amazon.com/images/I/61GsdjWeYnL._AC_US600_.jpg"/>
+    <hyperlink ref="L43" r:id="rId312" tooltip="https://www.amazon.co.uk/dp/B0G1YQ9T93"/>
+    <hyperlink ref="M43" r:id="rId313" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N43" r:id="rId314"/>
+    <hyperlink ref="C44" r:id="rId315" tooltip="https://www.amazon.co.uk/dp/B0FH4QN7S1"/>
+    <hyperlink ref="G44" r:id="rId316" tooltip="https://www.amazon.co.uk/stores/Akitas/page/BE01E01C-FB27-4053-9F09-4CEDBCF3376A?lp_asin=B0FH4QN7S1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J44" r:id="rId317" tooltip="https://www.amazon.co.uk/dp/B0FH4QN7S1?psc=1"/>
+    <hyperlink ref="K44" r:id="rId318" tooltip="https://images-na.ssl-images-amazon.com/images/I/61iXQi6Bc8L._AC_US600_.jpg"/>
+    <hyperlink ref="L44" r:id="rId319" tooltip="https://www.amazon.co.uk/dp/B0FH4QN7S1"/>
     <hyperlink ref="M44" r:id="rId320" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
     <hyperlink ref="N44" r:id="rId321"/>
-    <hyperlink ref="C45" r:id="rId322" tooltip="https://www.amazon.co.uk/dp/B0FH4QN7S1"/>
-    <hyperlink ref="G45" r:id="rId323" tooltip="https://www.amazon.co.uk/stores/Akitas/page/BE01E01C-FB27-4053-9F09-4CEDBCF3376A?lp_asin=B0FH4QN7S1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J45" r:id="rId324" tooltip="https://www.amazon.co.uk/dp/B0FH4QN7S1?psc=1"/>
-    <hyperlink ref="K45" r:id="rId325" tooltip="https://images-na.ssl-images-amazon.com/images/I/61iXQi6Bc8L._AC_US600_.jpg"/>
-    <hyperlink ref="L45" r:id="rId326" tooltip="https://www.amazon.co.uk/dp/B0FH4QN7S1"/>
-    <hyperlink ref="M45" r:id="rId327" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N45" r:id="rId328"/>
-    <hyperlink ref="AW45" r:id="rId329" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P"/>
-    <hyperlink ref="C46" r:id="rId330" tooltip="https://www.amazon.co.uk/dp/B0FT7BQ1P4"/>
-    <hyperlink ref="G46" r:id="rId331" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=SUXIANGVAC"/>
-    <hyperlink ref="J46" r:id="rId332" tooltip="https://www.amazon.co.uk/dp/B0FT7BQ1P4?psc=1"/>
-    <hyperlink ref="K46" r:id="rId333" tooltip="https://images-na.ssl-images-amazon.com/images/I/81q6iYg2xZL._AC_US600_.jpg"/>
-    <hyperlink ref="L46" r:id="rId334" tooltip="https://www.amazon.co.uk/dp/B0FT7BQ1P4"/>
-    <hyperlink ref="M46" r:id="rId335" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N46" r:id="rId336"/>
-    <hyperlink ref="AW46" r:id="rId337" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A30X0O348OEO2T"/>
-    <hyperlink ref="C47" r:id="rId338" tooltip="https://www.amazon.co.uk/dp/B0HF818ZJD"/>
-    <hyperlink ref="G47" r:id="rId339" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Honiture+Clean"/>
-    <hyperlink ref="J47" r:id="rId340" tooltip="https://www.amazon.co.uk/dp/B0HF818ZJD?psc=1"/>
-    <hyperlink ref="K47" r:id="rId341" tooltip="https://images-na.ssl-images-amazon.com/images/I/71p1cQ8K3nL._AC_US600_.jpg"/>
-    <hyperlink ref="L47" r:id="rId342" tooltip="https://www.amazon.co.uk/dp/B0HF818ZJD"/>
-    <hyperlink ref="M47" r:id="rId343" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N47" r:id="rId344"/>
-    <hyperlink ref="AW47" r:id="rId345" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AHXM9EXJUYAPG"/>
-    <hyperlink ref="C48" r:id="rId346" tooltip="https://www.amazon.co.uk/dp/B0FSF6XG22"/>
-    <hyperlink ref="G48" r:id="rId347" tooltip="https://www.amazon.co.uk/stores/OlsenSmith/page/1FA1F547-221C-40C6-BA4F-6E13B39F7CE1?lp_asin=B0FSF6XG22&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J48" r:id="rId348" tooltip="https://www.amazon.co.uk/dp/B0FSF6XG22?psc=1"/>
-    <hyperlink ref="K48" r:id="rId349" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41cxjopmqiL._AC_US600_.jpg"/>
-    <hyperlink ref="L48" r:id="rId350" tooltip="https://www.amazon.co.uk/dp/B0FSF6XG22"/>
-    <hyperlink ref="M48" r:id="rId351" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N48" r:id="rId352"/>
-    <hyperlink ref="AW48" r:id="rId353" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3DJDH6QTTYBC6"/>
-    <hyperlink ref="C49" r:id="rId354" tooltip="https://www.amazon.co.uk/dp/B0C37SVX2V"/>
-    <hyperlink ref="G49" r:id="rId355" tooltip="https://www.amazon.co.uk/stores/Duronic/page/A5A8FDD3-4203-4BE8-BCF2-850400F720CD?lp_asin=B0C37SVX2V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J49" r:id="rId356" tooltip="https://www.amazon.co.uk/dp/B0C37SVX2V?psc=1"/>
-    <hyperlink ref="K49" r:id="rId357" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51+CY4t2PIL._AC_US600_.jpg"/>
-    <hyperlink ref="L49" r:id="rId358" tooltip="https://www.amazon.co.uk/dp/B0C37SVX2V"/>
-    <hyperlink ref="M49" r:id="rId359" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N49" r:id="rId360"/>
-    <hyperlink ref="AW49" r:id="rId361" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=APLJ5AXPSKRV0"/>
-    <hyperlink ref="C50" r:id="rId362" tooltip="https://www.amazon.co.uk/dp/B0FGPM83WQ"/>
-    <hyperlink ref="G50" r:id="rId363" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Vlihapy"/>
-    <hyperlink ref="J50" r:id="rId364" tooltip="https://www.amazon.co.uk/dp/B0FGPM83WQ?psc=1"/>
-    <hyperlink ref="K50" r:id="rId365" tooltip="https://images-na.ssl-images-amazon.com/images/I/61YPwkc2MmL._AC_US600_.jpg"/>
-    <hyperlink ref="L50" r:id="rId366" tooltip="https://www.amazon.co.uk/dp/B0FGPM83WQ"/>
-    <hyperlink ref="M50" r:id="rId367" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N50" r:id="rId368"/>
-    <hyperlink ref="AW50" r:id="rId369" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KUVQEB99D827"/>
-    <hyperlink ref="C51" r:id="rId370" tooltip="https://www.amazon.co.uk/dp/B07ZQH4T3T"/>
-    <hyperlink ref="G51" r:id="rId371" tooltip="https://www.amazon.co.uk/stores/JML/page/7D82F081-93D9-4B24-9DE9-D18ADF17C695?lp_asin=B07ZQH4T3T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J51" r:id="rId372" tooltip="https://www.amazon.co.uk/dp/B07ZQH4T3T?psc=1"/>
-    <hyperlink ref="K51" r:id="rId373" tooltip="https://images-na.ssl-images-amazon.com/images/I/81IMjIncpDL._AC_US600_.jpg"/>
-    <hyperlink ref="L51" r:id="rId374" tooltip="https://www.amazon.co.uk/dp/B07ZQH4T3T"/>
-    <hyperlink ref="M51" r:id="rId375" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N51" r:id="rId376"/>
-    <hyperlink ref="AW51" r:id="rId377" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KNWE4UE7YTH1"/>
+    <hyperlink ref="AW44" r:id="rId322" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P"/>
+    <hyperlink ref="C45" r:id="rId323" tooltip="https://www.amazon.co.uk/dp/B0FT7BQ1P4"/>
+    <hyperlink ref="G45" r:id="rId324" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=SUXIANGVAC"/>
+    <hyperlink ref="J45" r:id="rId325" tooltip="https://www.amazon.co.uk/dp/B0FT7BQ1P4?psc=1"/>
+    <hyperlink ref="K45" r:id="rId326" tooltip="https://images-na.ssl-images-amazon.com/images/I/81q6iYg2xZL._AC_US600_.jpg"/>
+    <hyperlink ref="L45" r:id="rId327" tooltip="https://www.amazon.co.uk/dp/B0FT7BQ1P4"/>
+    <hyperlink ref="M45" r:id="rId328" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N45" r:id="rId329"/>
+    <hyperlink ref="AW45" r:id="rId330" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A30X0O348OEO2T"/>
+    <hyperlink ref="C46" r:id="rId331" tooltip="https://www.amazon.co.uk/dp/B0HF818ZJD"/>
+    <hyperlink ref="G46" r:id="rId332" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Honiture+Clean"/>
+    <hyperlink ref="J46" r:id="rId333" tooltip="https://www.amazon.co.uk/dp/B0HF818ZJD?psc=1"/>
+    <hyperlink ref="K46" r:id="rId334" tooltip="https://images-na.ssl-images-amazon.com/images/I/71p1cQ8K3nL._AC_US600_.jpg"/>
+    <hyperlink ref="L46" r:id="rId335" tooltip="https://www.amazon.co.uk/dp/B0HF818ZJD"/>
+    <hyperlink ref="M46" r:id="rId336" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N46" r:id="rId337"/>
+    <hyperlink ref="AW46" r:id="rId338" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AHXM9EXJUYAPG"/>
+    <hyperlink ref="C47" r:id="rId339" tooltip="https://www.amazon.co.uk/dp/B0FSF6XG22"/>
+    <hyperlink ref="G47" r:id="rId340" tooltip="https://www.amazon.co.uk/stores/OlsenSmith/page/1FA1F547-221C-40C6-BA4F-6E13B39F7CE1?lp_asin=B0FSF6XG22&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J47" r:id="rId341" tooltip="https://www.amazon.co.uk/dp/B0FSF6XG22?psc=1"/>
+    <hyperlink ref="K47" r:id="rId342" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41cxjopmqiL._AC_US600_.jpg"/>
+    <hyperlink ref="L47" r:id="rId343" tooltip="https://www.amazon.co.uk/dp/B0FSF6XG22"/>
+    <hyperlink ref="M47" r:id="rId344" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N47" r:id="rId345"/>
+    <hyperlink ref="AW47" r:id="rId346" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3DJDH6QTTYBC6"/>
+    <hyperlink ref="C48" r:id="rId347" tooltip="https://www.amazon.co.uk/dp/B0C37SVX2V"/>
+    <hyperlink ref="G48" r:id="rId348" tooltip="https://www.amazon.co.uk/stores/Duronic/page/A5A8FDD3-4203-4BE8-BCF2-850400F720CD?lp_asin=B0C37SVX2V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J48" r:id="rId349" tooltip="https://www.amazon.co.uk/dp/B0C37SVX2V?psc=1"/>
+    <hyperlink ref="K48" r:id="rId350" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/51+CY4t2PIL._AC_US600_.jpg"/>
+    <hyperlink ref="L48" r:id="rId351" tooltip="https://www.amazon.co.uk/dp/B0C37SVX2V"/>
+    <hyperlink ref="M48" r:id="rId352" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N48" r:id="rId353"/>
+    <hyperlink ref="AW48" r:id="rId354" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=APLJ5AXPSKRV0"/>
+    <hyperlink ref="C49" r:id="rId355" tooltip="https://www.amazon.co.uk/dp/B0FGPM83WQ"/>
+    <hyperlink ref="G49" r:id="rId356" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Vlihapy"/>
+    <hyperlink ref="J49" r:id="rId357" tooltip="https://www.amazon.co.uk/dp/B0FGPM83WQ?psc=1"/>
+    <hyperlink ref="K49" r:id="rId358" tooltip="https://images-na.ssl-images-amazon.com/images/I/61YPwkc2MmL._AC_US600_.jpg"/>
+    <hyperlink ref="L49" r:id="rId359" tooltip="https://www.amazon.co.uk/dp/B0FGPM83WQ"/>
+    <hyperlink ref="M49" r:id="rId360" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N49" r:id="rId361"/>
+    <hyperlink ref="AW49" r:id="rId362" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KUVQEB99D827"/>
+    <hyperlink ref="C50" r:id="rId363" tooltip="https://www.amazon.co.uk/dp/B07ZQH4T3T"/>
+    <hyperlink ref="G50" r:id="rId364" tooltip="https://www.amazon.co.uk/stores/JML/page/7D82F081-93D9-4B24-9DE9-D18ADF17C695?lp_asin=B07ZQH4T3T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J50" r:id="rId365" tooltip="https://www.amazon.co.uk/dp/B07ZQH4T3T?psc=1"/>
+    <hyperlink ref="K50" r:id="rId366" tooltip="https://images-na.ssl-images-amazon.com/images/I/81IMjIncpDL._AC_US600_.jpg"/>
+    <hyperlink ref="L50" r:id="rId367" tooltip="https://www.amazon.co.uk/dp/B07ZQH4T3T"/>
+    <hyperlink ref="M50" r:id="rId368" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N50" r:id="rId369"/>
+    <hyperlink ref="AW50" r:id="rId370" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KNWE4UE7YTH1"/>
   </hyperlinks>
-  <drawing r:id="rId378"/>
+  <drawing r:id="rId371"/>
 </worksheet>
 </file>
 
@@ -19797,18 +19520,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>11131</v>
+        <v>9117</v>
       </c>
       <c r="C2" s="15">
-        <v>2311363</v>
+        <v>2281173</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>207.6509747551882</v>
+        <v>250.21092464626523</v>
       </c>
       <c r="G2" s="22">
-        <v>0.24917174068767908</v>
+        <v>0.21372310000468844</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19829,7 +19552,7 @@
         <v>335.0713958810069</v>
       </c>
       <c r="G3" s="22">
-        <v>0.04891207020057307</v>
+        <v>0.05122134183506025</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19850,7 +19573,7 @@
         <v>114.48323397913562</v>
       </c>
       <c r="G4" s="22">
-        <v>0.0600823782234957</v>
+        <v>0.0629190304280557</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19871,7 +19594,7 @@
         <v>63.249941107184924</v>
       </c>
       <c r="G5" s="22">
-        <v>0.09502596704871061</v>
+        <v>0.09951240095644427</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19892,7 +19615,7 @@
         <v>69.02606502242152</v>
       </c>
       <c r="G6" s="22">
-        <v>0.07987106017191978</v>
+        <v>0.08364198977917389</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19913,7 +19636,7 @@
         <v>119.99010989010989</v>
       </c>
       <c r="G7" s="22">
-        <v>0.04074140401146132</v>
+        <v>0.0426649163111257</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19934,7 +19657,7 @@
         <v>239.0</v>
       </c>
       <c r="G8" s="22">
-        <v>0.019788681948424067</v>
+        <v>0.020722959351118196</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19955,7 +19678,7 @@
         <v>57.46141732283465</v>
       </c>
       <c r="G9" s="22">
-        <v>0.07107360315186247</v>
+        <v>0.07442918092737587</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19976,7 +19699,7 @@
         <v>169.99006951340616</v>
       </c>
       <c r="G10" s="22">
-        <v>0.02254208452722063</v>
+        <v>0.02360635754137559</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19997,7 +19720,7 @@
         <v>133.58572600492207</v>
       </c>
       <c r="G11" s="22">
-        <v>0.02728778653295129</v>
+        <v>0.028576117023770452</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20018,7 +19741,7 @@
         <v>113.9895337773549</v>
       </c>
       <c r="G12" s="22">
-        <v>0.023527041547277937</v>
+        <v>0.02463781705658962</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20039,7 +19762,7 @@
         <v>149.9754601226994</v>
       </c>
       <c r="G13" s="22">
-        <v>0.014595272206303725</v>
+        <v>0.01528435463453514</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20060,7 +19783,7 @@
         <v>67.98986975397973</v>
       </c>
       <c r="G14" s="22">
-        <v>0.03093660458452722</v>
+        <v>0.032397205682404236</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20081,7 +19804,7 @@
         <v>219.0</v>
       </c>
       <c r="G15" s="22">
-        <v>0.00808112464183381</v>
+        <v>0.00846265647709691</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20102,7 +19825,7 @@
         <v>179.990099009901</v>
       </c>
       <c r="G16" s="22">
-        <v>0.009043696275071633</v>
+        <v>0.009470673730601528</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20123,7 +19846,7 @@
         <v>82.88505747126437</v>
       </c>
       <c r="G17" s="22">
-        <v>0.015580229226361032</v>
+        <v>0.01631581414974917</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20144,7 +19867,7 @@
         <v>199.0</v>
       </c>
       <c r="G18" s="22">
-        <v>0.005350107449856733</v>
+        <v>0.005602700548548924</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20165,7 +19888,7 @@
         <v>76.47960848287113</v>
       </c>
       <c r="G19" s="22">
-        <v>0.01372224212034384</v>
+        <v>0.014370106427868162</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20186,7 +19909,7 @@
         <v>61.989505247376314</v>
       </c>
       <c r="G20" s="22">
-        <v>0.014931053008595988</v>
+        <v>0.015635988560176287</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20207,7 +19930,7 @@
         <v>24.990031152647976</v>
       </c>
       <c r="G21" s="22">
-        <v>0.035928545845272206</v>
+        <v>0.037624830043602606</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20228,7 +19951,7 @@
         <v>67.98970840480274</v>
       </c>
       <c r="G22" s="22">
-        <v>0.013050680515759312</v>
+        <v>0.013666838576585868</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20249,7 +19972,7 @@
         <v>89.98062953995158</v>
       </c>
       <c r="G23" s="22">
-        <v>0.009245164756446992</v>
+        <v>0.009681654085986216</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20270,7 +19993,7 @@
         <v>33.990338164251206</v>
       </c>
       <c r="G24" s="22">
-        <v>0.02316887535816619</v>
+        <v>0.024262740869239064</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20291,7 +20014,7 @@
         <v>32.990059642147116</v>
       </c>
       <c r="G25" s="22">
-        <v>0.022519699140401146</v>
+        <v>0.023582915279666182</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20312,7 +20035,7 @@
         <v>129.99074074074073</v>
       </c>
       <c r="G26" s="22">
-        <v>0.004835243553008596</v>
+        <v>0.0050635285292325</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20333,7 +20056,7 @@
         <v>139.9889502762431</v>
       </c>
       <c r="G27" s="22">
-        <v>0.004051755014326647</v>
+        <v>0.0042430493694031604</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20354,7 +20077,7 @@
         <v>72.98876404494382</v>
       </c>
       <c r="G28" s="22">
-        <v>0.0059768982808022925</v>
+        <v>0.006259083876412396</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20375,7 +20098,7 @@
         <v>79.99038461538461</v>
       </c>
       <c r="G29" s="22">
-        <v>0.004656160458452722</v>
+        <v>0.004875990435557222</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20396,7 +20119,7 @@
         <v>49.99103139013453</v>
       </c>
       <c r="G30" s="22">
-        <v>0.004991941260744986</v>
+        <v>0.005227624361198368</v>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20417,7 +20140,7 @@
         <v>42.488461538461536</v>
       </c>
       <c r="G31" s="22">
-        <v>0.005820200573065902</v>
+        <v>0.006094988044446528</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20438,7 +20161,7 @@
         <v>31.979228486646885</v>
       </c>
       <c r="G32" s="22">
-        <v>0.007543875358166189</v>
+        <v>0.007900042196071077</v>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20459,7 +20182,7 @@
         <v>14.988732394366197</v>
       </c>
       <c r="G33" s="22">
-        <v>0.007946812320916905</v>
+        <v>0.008322002906840452</v>
       </c>
     </row>
   </sheetData>
@@ -20523,18 +20246,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>20864</v>
+        <v>18850</v>
       </c>
       <c r="C2" s="15">
-        <v>3554295</v>
+        <v>3524105</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>170.35539685582822</v>
+        <v>186.9551724137931</v>
       </c>
       <c r="G2" s="22">
-        <v>0.4670487106017192</v>
+        <v>0.4418866332223733</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20555,7 +20278,7 @@
         <v>63.249941107184924</v>
       </c>
       <c r="G3" s="22">
-        <v>0.09502596704871061</v>
+        <v>0.09951240095644427</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20576,7 +20299,7 @@
         <v>317.9899497487437</v>
       </c>
       <c r="G4" s="22">
-        <v>0.017818767908309455</v>
+        <v>0.01866004032069014</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20597,7 +20320,7 @@
         <v>419.0</v>
       </c>
       <c r="G5" s="22">
-        <v>0.012961138968481375</v>
+        <v>0.01357306952974823</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20618,7 +20341,7 @@
         <v>67.99018404907976</v>
       </c>
       <c r="G6" s="22">
-        <v>0.07297636103151862</v>
+        <v>0.0764217731726757</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20639,7 +20362,7 @@
         <v>119.99010989010989</v>
       </c>
       <c r="G7" s="22">
-        <v>0.04074140401146132</v>
+        <v>0.0426649163111257</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20660,7 +20383,7 @@
         <v>57.46141732283465</v>
       </c>
       <c r="G8" s="22">
-        <v>0.07107360315186247</v>
+        <v>0.07442918092737587</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20681,7 +20404,7 @@
         <v>169.99006951340616</v>
       </c>
       <c r="G9" s="22">
-        <v>0.02254208452722063</v>
+        <v>0.02360635754137559</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20702,7 +20425,7 @@
         <v>113.9895337773549</v>
       </c>
       <c r="G10" s="22">
-        <v>0.023527041547277937</v>
+        <v>0.02463781705658962</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20723,7 +20446,7 @@
         <v>67.98986975397973</v>
       </c>
       <c r="G11" s="22">
-        <v>0.03093660458452722</v>
+        <v>0.032397205682404236</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20744,7 +20467,7 @@
         <v>179.990099009901</v>
       </c>
       <c r="G12" s="22">
-        <v>0.009043696275071633</v>
+        <v>0.009470673730601528</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20765,7 +20488,7 @@
         <v>149.96995708154506</v>
       </c>
       <c r="G13" s="22">
-        <v>0.010431590257879656</v>
+        <v>0.010924093956584932</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20786,7 +20509,7 @@
         <v>199.0</v>
       </c>
       <c r="G14" s="22">
-        <v>0.005350107449856733</v>
+        <v>0.005602700548548924</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20807,7 +20530,7 @@
         <v>24.990031152647976</v>
       </c>
       <c r="G15" s="22">
-        <v>0.035928545845272206</v>
+        <v>0.037624830043602606</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20828,7 +20551,7 @@
         <v>89.98062953995158</v>
       </c>
       <c r="G16" s="22">
-        <v>0.009245164756446992</v>
+        <v>0.009681654085986216</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20849,7 +20572,7 @@
         <v>32.990059642147116</v>
       </c>
       <c r="G17" s="22">
-        <v>0.022519699140401146</v>
+        <v>0.023582915279666182</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20870,7 +20593,7 @@
         <v>129.99074074074073</v>
       </c>
       <c r="G18" s="22">
-        <v>0.004835243553008596</v>
+        <v>0.0050635285292325</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20891,7 +20614,7 @@
         <v>149.98924731182797</v>
       </c>
       <c r="G19" s="22">
-        <v>0.004163681948424069</v>
+        <v>0.0043602606779502085</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20912,7 +20635,7 @@
         <v>79.99025974025975</v>
       </c>
       <c r="G20" s="22">
-        <v>0.006894699140401146</v>
+        <v>0.007220216606498195</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20933,7 +20656,7 @@
         <v>72.98876404494382</v>
       </c>
       <c r="G21" s="22">
-        <v>0.0059768982808022925</v>
+        <v>0.006259083876412396</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20954,7 +20677,7 @@
         <v>79.99038461538461</v>
       </c>
       <c r="G22" s="22">
-        <v>0.004656160458452722</v>
+        <v>0.004875990435557222</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20975,7 +20698,7 @@
         <v>49.99103139013453</v>
       </c>
       <c r="G23" s="22">
-        <v>0.004991941260744986</v>
+        <v>0.005227624361198368</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20996,7 +20719,7 @@
         <v>42.488461538461536</v>
       </c>
       <c r="G24" s="22">
-        <v>0.005820200573065902</v>
+        <v>0.006094988044446528</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21017,7 +20740,7 @@
         <v>31.979228486646885</v>
       </c>
       <c r="G25" s="22">
-        <v>0.007543875358166189</v>
+        <v>0.007900042196071077</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21038,7 +20761,7 @@
         <v>14.988732394366197</v>
       </c>
       <c r="G26" s="22">
-        <v>0.007946812320916905</v>
+        <v>0.008322002906840452</v>
       </c>
     </row>
   </sheetData>
